--- a/public/Plantilla_Quimica_Bethel.xlsx
+++ b/public/Plantilla_Quimica_Bethel.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89D4877-11E7-47BF-9AD7-042A2BD0FC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -5605,12 +5605,6 @@
     <xf numFmtId="164" fontId="0" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5619,6 +5613,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5983,54 +5983,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
     </row>
     <row r="2" spans="1:21" ht="32" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
     </row>
     <row r="4" spans="1:21" ht="34" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -38113,34 +38113,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="49" t="s">
         <v>1701</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
       <c r="K1" s="33"/>
       <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="50" t="s">
         <v>1702</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
       <c r="K2" s="34"/>
       <c r="L2" s="34"/>
     </row>
@@ -38172,13 +38172,13 @@
         <v>1706</v>
       </c>
       <c r="E4" s="37"/>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="51" t="s">
         <v>1707</v>
       </c>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
       <c r="K4" s="37"/>
       <c r="L4" s="37"/>
     </row>
@@ -47460,11 +47460,11 @@
         <v>14190</v>
       </c>
       <c r="K207" s="46">
-        <f t="shared" ref="K207:K270" si="34">IF(J207="","",J207-B207-E207-F207-G207-(J207*H207))</f>
+        <f t="shared" ref="K207:K250" si="34">IF(J207="","",J207-B207-E207-F207-G207-(J207*H207))</f>
         <v>5675.1408000000001</v>
       </c>
       <c r="L207" s="48">
-        <f t="shared" ref="L207:L270" si="35">IF(J207="","",K207/J207)</f>
+        <f t="shared" ref="L207:L250" si="35">IF(J207="","",K207/J207)</f>
         <v>0.39993945031712475</v>
       </c>
     </row>
@@ -58698,23 +58698,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="52" t="s">
         <v>1322</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
     </row>
     <row r="2" spans="1:15" ht="32" customHeight="1">
       <c r="A2" s="54" t="s">

--- a/public/Plantilla_Quimica_Bethel.xlsx
+++ b/public/Plantilla_Quimica_Bethel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\QUIMICA - V3\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89D4877-11E7-47BF-9AD7-042A2BD0FC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF648840-E89C-43D1-A3B0-3E4DDD1A8231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -5605,6 +5605,12 @@
     <xf numFmtId="164" fontId="0" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5613,12 +5619,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5983,54 +5983,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" ht="32" customHeight="1">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
     </row>
     <row r="4" spans="1:21" ht="34" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -38113,34 +38113,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>1701</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
       <c r="K1" s="33"/>
       <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="52" t="s">
         <v>1702</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
       <c r="K2" s="34"/>
       <c r="L2" s="34"/>
     </row>
@@ -38172,13 +38172,13 @@
         <v>1706</v>
       </c>
       <c r="E4" s="37"/>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="53" t="s">
         <v>1707</v>
       </c>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
       <c r="K4" s="37"/>
       <c r="L4" s="37"/>
     </row>
@@ -58698,23 +58698,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="49" t="s">
         <v>1322</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
     </row>
     <row r="2" spans="1:15" ht="32" customHeight="1">
       <c r="A2" s="54" t="s">
@@ -59294,13 +59294,12 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="30" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(B18="","","CAT-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
       </c>
-      <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="19" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(B18="","",IF(COUNTIF($B$6:$B$105,B18)&gt;1,"REVISAR: DUPLICADA","OK"))</f>
         <v/>
       </c>
       <c r="F17" s="30" t="str">
@@ -59334,15 +59333,15 @@
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="30" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A18" s="30" t="e">
+        <f>IF(#REF!="","","CAT-"&amp;TEXT(ROW()-5,"000"))</f>
+        <v>#REF!</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="19" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="D18" s="19" t="e">
+        <f>IF(#REF!="","",IF(COUNTIF($B$6:$B$105,#REF!)&gt;1,"REVISAR: DUPLICADA","OK"))</f>
+        <v>#REF!</v>
       </c>
       <c r="F18" s="30" t="str">
         <f t="shared" si="2"/>

--- a/public/Plantilla_Quimica_Bethel.xlsx
+++ b/public/Plantilla_Quimica_Bethel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\QUIMICA - V3\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B825C5A-E976-4F9B-A51C-91AED871FDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B34C36-5192-4460-908E-A42289DC962A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5611,12 +5611,6 @@
     <xf numFmtId="164" fontId="0" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5625,6 +5619,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5989,54 +5989,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
     </row>
     <row r="2" spans="1:21" ht="32" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
     </row>
     <row r="4" spans="1:21" ht="34" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -38119,34 +38119,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="49" t="s">
         <v>1699</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
       <c r="K1" s="33"/>
       <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="50" t="s">
         <v>1700</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
       <c r="K2" s="34"/>
       <c r="L2" s="34"/>
     </row>
@@ -38178,13 +38178,13 @@
         <v>1704</v>
       </c>
       <c r="E4" s="37"/>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="51" t="s">
         <v>1705</v>
       </c>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
       <c r="K4" s="37"/>
       <c r="L4" s="37"/>
     </row>
@@ -38419,11 +38419,11 @@
         <v>1735</v>
       </c>
       <c r="D15" s="41">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E15" s="46">
         <f t="shared" ref="E15:E78" si="0">IF(A15="","",IF(C15="NO",0,IF(D15&lt;&gt;"",D15,$B$11)))</f>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F15" s="46">
         <f t="shared" ref="F15:F78" si="1">IF(A15="","",$B$7/$B$6)</f>
@@ -38443,15 +38443,15 @@
       </c>
       <c r="J15" s="46">
         <f t="shared" ref="J15:J78" si="5">IF(OR(A15="",B15=""),"",ROUND((B15+E15+F15+G15)/(1-H15-I15),-1))</f>
-        <v>2650</v>
+        <v>4150</v>
       </c>
       <c r="K15" s="46">
         <f t="shared" ref="K15:K78" si="6">IF(J15="","",J15-B15-E15-F15-G15-(J15*H15))</f>
-        <v>872.5</v>
+        <v>1372.5</v>
       </c>
       <c r="L15" s="48">
         <f t="shared" ref="L15:L78" si="7">IF(J15="","",K15/J15)</f>
-        <v>0.32924528301886791</v>
+        <v>0.33072289156626505</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -39063,7 +39063,7 @@
         <v>34</v>
       </c>
       <c r="D29" s="44">
-        <f t="shared" ref="D15:D78" si="8">IF(A29="","",$B$7/$B$6)</f>
+        <f t="shared" ref="D29:D78" si="8">IF(A29="","",$B$7/$B$6)</f>
         <v>250</v>
       </c>
       <c r="E29" s="46">
@@ -41411,7 +41411,7 @@
         <v>34</v>
       </c>
       <c r="D79" s="44">
-        <f t="shared" ref="D79:D142" si="9">IF(A79="","",$B$7/$B$6)</f>
+        <f t="shared" ref="D79:D140" si="9">IF(A79="","",$B$7/$B$6)</f>
         <v>250</v>
       </c>
       <c r="E79" s="46">
@@ -45695,7 +45695,7 @@
         <v>34</v>
       </c>
       <c r="D171" s="44">
-        <f t="shared" ref="D143:D206" si="26">IF(A171="","",$B$7/$B$6)</f>
+        <f t="shared" ref="D171:D206" si="26">IF(A171="","",$B$7/$B$6)</f>
         <v>250</v>
       </c>
       <c r="E171" s="46">
@@ -58651,23 +58651,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="52" t="s">
         <v>1322</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
     </row>
     <row r="2" spans="1:15" ht="32" customHeight="1">
       <c r="A2" s="54" t="s">

--- a/public/Plantilla_Quimica_Bethel.xlsx
+++ b/public/Plantilla_Quimica_Bethel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\QUIMICA - V3\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98525B5D-8A2C-4C4E-8BC4-6D771FFFE46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51151F68-B5BB-42E7-9C32-C2682AC73049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -5608,6 +5608,18 @@
     <xf numFmtId="164" fontId="0" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5616,18 +5628,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5986,54 +5986,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" ht="32" customHeight="1">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
     </row>
     <row r="4" spans="1:21" ht="34" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -38116,34 +38116,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="53" t="s">
         <v>1695</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
       <c r="K1" s="33"/>
       <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="54" t="s">
         <v>1696</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
       <c r="K2" s="34"/>
       <c r="L2" s="34"/>
     </row>
@@ -38175,13 +38175,13 @@
         <v>1700</v>
       </c>
       <c r="E4" s="37"/>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="55" t="s">
         <v>1701</v>
       </c>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
       <c r="K4" s="37"/>
       <c r="L4" s="37"/>
     </row>
@@ -38473,7 +38473,7 @@
         <v>25</v>
       </c>
       <c r="G16" s="46">
-        <f t="shared" ref="G15:G78" si="7">IF(A16="","",($B$8-$B$9)/$B$6)</f>
+        <f t="shared" ref="G16:G78" si="7">IF(A16="","",($B$8-$B$9)/$B$6)</f>
         <v>0</v>
       </c>
       <c r="H16" s="47">
@@ -49351,7 +49351,7 @@
         <v>1314</v>
       </c>
       <c r="B249" s="44">
-        <v>2600</v>
+        <v>1600</v>
       </c>
       <c r="C249" s="45" t="s">
         <v>1731</v>
@@ -49381,15 +49381,15 @@
       </c>
       <c r="J249" s="46">
         <f t="shared" si="33"/>
-        <v>5430</v>
+        <v>3940</v>
       </c>
       <c r="K249" s="46">
         <f t="shared" si="34"/>
-        <v>1805</v>
+        <v>1315</v>
       </c>
       <c r="L249" s="48">
         <f t="shared" si="35"/>
-        <v>0.33241252302025781</v>
+        <v>0.33375634517766495</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -58648,63 +58648,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="49" t="s">
         <v>1322</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
     </row>
     <row r="2" spans="1:15" ht="32" customHeight="1">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="50" t="s">
         <v>1323</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="51" t="s">
         <v>1324</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="F4" s="55" t="s">
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="F4" s="51" t="s">
         <v>1325</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="L4" s="55" t="s">
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="L4" s="51" t="s">
         <v>1326</v>
       </c>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
     </row>
     <row r="5" spans="1:15" ht="28">
       <c r="A5" s="2" t="s">

--- a/public/Plantilla_Quimica_Bethel.xlsx
+++ b/public/Plantilla_Quimica_Bethel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\QUIMICA - V3\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631A36DD-DD5C-4C63-AE48-F88032994FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9E27BF-4DB6-4D3D-B697-916BDB1377C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="11500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6514" uniqueCount="1811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6636" uniqueCount="1838">
   <si>
     <t>CATÁLOGO DE PRODUCTOS · CARGA ADMINISTRATIVA</t>
   </si>
@@ -5153,9 +5153,6 @@
     <t>Esponja dorada. Presentación: 1 unidad.</t>
   </si>
   <si>
-    <t>Lavandina al 4%. Presentación: 1 litros.</t>
-  </si>
-  <si>
     <t>Control de fotos del catálogo</t>
   </si>
   <si>
@@ -5472,6 +5469,90 @@
   </si>
   <si>
     <t>Generador 1</t>
+  </si>
+  <si>
+    <t>Papel Simple Hoja Higienico pack de 30 rollos x 80m</t>
+  </si>
+  <si>
+    <t>New Pel</t>
+  </si>
+  <si>
+    <t>VAR010.jpg</t>
+  </si>
+  <si>
+    <t>CNT-228</t>
+  </si>
+  <si>
+    <t>VAR010</t>
+  </si>
+  <si>
+    <t>Papel Simple Hoja Higienico pack de 30 rollos x 30m</t>
+  </si>
+  <si>
+    <t>VAR011.jpg</t>
+  </si>
+  <si>
+    <t>VAR011</t>
+  </si>
+  <si>
+    <t>Papel Doble Hoja Higienico pack de 12 rollos x 30m</t>
+  </si>
+  <si>
+    <t>VAR012.jpg</t>
+  </si>
+  <si>
+    <t>VAR012</t>
+  </si>
+  <si>
+    <t>Papel Doble Hoja Higienico pack de 30 rollos x 30m</t>
+  </si>
+  <si>
+    <t>VAR013.jpg</t>
+  </si>
+  <si>
+    <t>VAR013</t>
+  </si>
+  <si>
+    <t>Papel Triple Hoja Higienico pack de 10 rollos x 30m</t>
+  </si>
+  <si>
+    <t>VAR014.jpg</t>
+  </si>
+  <si>
+    <t>VAR014</t>
+  </si>
+  <si>
+    <t>Papel Bobina  pack de 2 rollos x 400m</t>
+  </si>
+  <si>
+    <t>Generico</t>
+  </si>
+  <si>
+    <t>VAR015.jpg</t>
+  </si>
+  <si>
+    <t>VAR015</t>
+  </si>
+  <si>
+    <t>Papel Jumbo pack de 8 rollos x 200m</t>
+  </si>
+  <si>
+    <t>VAR016.jpg</t>
+  </si>
+  <si>
+    <t>VAR016</t>
+  </si>
+  <si>
+    <t>Papel de cocina pack de 8 rollos x 150m</t>
+  </si>
+  <si>
+    <t>Pack de 8 Rollos de 150 metros: mayor rendimiento en cada compra. Pre corte facilita el uso y evita desperdicios. Textura suave para una experiencia agradable y delicada</t>
+  </si>
+  <si>
+    <t>VAR017.jpg</t>
+  </si>
+  <si>
+    <t>VAR017</t>
   </si>
 </sst>
 </file>
@@ -5958,6 +6039,7 @@
     <xf numFmtId="164" fontId="0" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="10" fillId="16" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5994,7 +6076,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="16" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6036,7 +6117,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProductosAdmin" displayName="ProductosAdmin" ref="A4:U1007" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProductosAdmin" displayName="ProductosAdmin" ref="A4:U1015" totalsRowShown="0">
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CODIGO"/>
@@ -6065,8 +6146,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PreciosPorProducto" displayName="PreciosPorProducto" ref="A14:L253" totalsRowShown="0">
-  <autoFilter ref="A14:L253" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PreciosPorProducto" displayName="PreciosPorProducto" ref="A14:L261" totalsRowShown="0">
+  <autoFilter ref="A14:L261" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CODIGO"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="COSTO"/>
@@ -6330,7 +6411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1007"/>
+  <dimension ref="A1:U1015"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -6352,54 +6433,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30" customHeight="1">
-      <c r="A1" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
     </row>
     <row r="2" spans="1:21" ht="32" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70"/>
     </row>
     <row r="4" spans="1:21" ht="34" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -38445,108 +38526,60 @@
       <c r="U1004" s="11"/>
     </row>
     <row r="1005" spans="1:21">
-      <c r="A1005" s="7">
-        <v>237</v>
-      </c>
-      <c r="B1005" s="8" t="s">
-        <v>1809</v>
-      </c>
-      <c r="C1005" s="8" t="s">
-        <v>1809</v>
-      </c>
+      <c r="A1005" s="7"/>
+      <c r="B1005" s="8"/>
+      <c r="C1005" s="8"/>
       <c r="D1005" s="8"/>
       <c r="E1005" s="8"/>
-      <c r="F1005" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F1005" s="8"/>
       <c r="G1005" s="14"/>
-      <c r="H1005" s="8" t="s">
-        <v>26</v>
-      </c>
+      <c r="H1005" s="8"/>
       <c r="I1005" s="14"/>
-      <c r="J1005" s="8" t="s">
-        <v>1805</v>
-      </c>
-      <c r="K1005" s="8" t="s">
-        <v>1807</v>
-      </c>
+      <c r="J1005" s="8"/>
+      <c r="K1005" s="8"/>
       <c r="L1005" s="8"/>
-      <c r="M1005" s="8" t="s">
-        <v>1806</v>
-      </c>
-      <c r="N1005" s="8" t="s">
-        <v>1808</v>
-      </c>
-      <c r="O1005" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="M1005" s="8"/>
+      <c r="N1005" s="8"/>
+      <c r="O1005" s="8"/>
       <c r="P1005" s="14"/>
       <c r="Q1005" s="14"/>
       <c r="R1005" s="17"/>
       <c r="S1005" s="17"/>
-      <c r="T1005" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="U1005" s="11" t="s">
-        <v>34</v>
-      </c>
+      <c r="T1005" s="8"/>
+      <c r="U1005" s="11"/>
     </row>
     <row r="1006" spans="1:21">
-      <c r="A1006" s="7">
-        <v>237</v>
-      </c>
-      <c r="B1006" s="8" t="s">
-        <v>1809</v>
-      </c>
-      <c r="C1006" s="8" t="s">
-        <v>1809</v>
-      </c>
+      <c r="A1006" s="7"/>
+      <c r="B1006" s="8"/>
+      <c r="C1006" s="8"/>
       <c r="D1006" s="8"/>
       <c r="E1006" s="8"/>
-      <c r="F1006" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F1006" s="8"/>
       <c r="G1006" s="14"/>
-      <c r="H1006" s="8" t="s">
-        <v>26</v>
-      </c>
+      <c r="H1006" s="8"/>
       <c r="I1006" s="14"/>
-      <c r="J1006" s="8" t="s">
-        <v>1805</v>
-      </c>
-      <c r="K1006" s="8" t="s">
-        <v>1807</v>
-      </c>
+      <c r="J1006" s="8"/>
+      <c r="K1006" s="8"/>
       <c r="L1006" s="8"/>
-      <c r="M1006" s="8" t="s">
-        <v>1806</v>
-      </c>
-      <c r="N1006" s="8" t="s">
-        <v>1808</v>
-      </c>
-      <c r="O1006" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="M1006" s="8"/>
+      <c r="N1006" s="8"/>
+      <c r="O1006" s="8"/>
       <c r="P1006" s="14"/>
       <c r="Q1006" s="14"/>
       <c r="R1006" s="17"/>
       <c r="S1006" s="17"/>
-      <c r="T1006" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="U1006" s="11" t="s">
-        <v>34</v>
-      </c>
+      <c r="T1006" s="8"/>
+      <c r="U1006" s="11"/>
     </row>
     <row r="1007" spans="1:21">
       <c r="A1007" s="7">
         <v>237</v>
       </c>
       <c r="B1007" s="8" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="C1007" s="8" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="D1007" s="8"/>
       <c r="E1007" s="8"/>
@@ -38559,17 +38592,17 @@
       </c>
       <c r="I1007" s="14"/>
       <c r="J1007" s="8" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="K1007" s="8" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="L1007" s="8"/>
       <c r="M1007" s="8" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="N1007" s="8" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="O1007" s="8" t="s">
         <v>32</v>
@@ -38585,16 +38618,392 @@
         <v>34</v>
       </c>
     </row>
+    <row r="1008" spans="1:21">
+      <c r="A1008" s="7">
+        <v>237</v>
+      </c>
+      <c r="B1008" s="8" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C1008" s="8" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D1008" s="8"/>
+      <c r="E1008" s="8"/>
+      <c r="F1008" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1008" s="14"/>
+      <c r="H1008" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I1008" s="14"/>
+      <c r="J1008" s="8" t="s">
+        <v>1811</v>
+      </c>
+      <c r="K1008" s="8" t="s">
+        <v>1810</v>
+      </c>
+      <c r="L1008" s="8"/>
+      <c r="M1008" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1008" s="8" t="s">
+        <v>1812</v>
+      </c>
+      <c r="O1008" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1008" s="14"/>
+      <c r="Q1008" s="14"/>
+      <c r="R1008" s="17"/>
+      <c r="S1008" s="17"/>
+      <c r="T1008" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1008" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:21">
+      <c r="A1009" s="7">
+        <v>238</v>
+      </c>
+      <c r="B1009" s="8" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C1009" s="8" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D1009" s="8"/>
+      <c r="E1009" s="8"/>
+      <c r="F1009" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1009" s="14"/>
+      <c r="H1009" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I1009" s="14"/>
+      <c r="J1009" s="8" t="s">
+        <v>1811</v>
+      </c>
+      <c r="K1009" s="8" t="s">
+        <v>1815</v>
+      </c>
+      <c r="L1009" s="8"/>
+      <c r="M1009" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1009" s="8" t="s">
+        <v>1816</v>
+      </c>
+      <c r="O1009" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1009" s="14"/>
+      <c r="Q1009" s="14"/>
+      <c r="R1009" s="17"/>
+      <c r="S1009" s="17"/>
+      <c r="T1009" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1009" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:21">
+      <c r="A1010" s="7">
+        <v>239</v>
+      </c>
+      <c r="B1010" s="8" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C1010" s="8" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D1010" s="8"/>
+      <c r="E1010" s="8"/>
+      <c r="F1010" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1010" s="14"/>
+      <c r="H1010" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I1010" s="14"/>
+      <c r="J1010" s="8" t="s">
+        <v>1811</v>
+      </c>
+      <c r="K1010" s="8" t="s">
+        <v>1818</v>
+      </c>
+      <c r="L1010" s="8"/>
+      <c r="M1010" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1010" s="8" t="s">
+        <v>1819</v>
+      </c>
+      <c r="O1010" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1010" s="14"/>
+      <c r="Q1010" s="14"/>
+      <c r="R1010" s="17"/>
+      <c r="S1010" s="17"/>
+      <c r="T1010" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1010" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:21">
+      <c r="A1011" s="7">
+        <v>240</v>
+      </c>
+      <c r="B1011" s="8" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C1011" s="8" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D1011" s="8"/>
+      <c r="E1011" s="8"/>
+      <c r="F1011" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1011" s="14"/>
+      <c r="H1011" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I1011" s="14"/>
+      <c r="J1011" s="8" t="s">
+        <v>1811</v>
+      </c>
+      <c r="K1011" s="8" t="s">
+        <v>1821</v>
+      </c>
+      <c r="L1011" s="8"/>
+      <c r="M1011" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1011" s="8" t="s">
+        <v>1822</v>
+      </c>
+      <c r="O1011" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1011" s="14"/>
+      <c r="Q1011" s="14"/>
+      <c r="R1011" s="17"/>
+      <c r="S1011" s="17"/>
+      <c r="T1011" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1011" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:21">
+      <c r="A1012" s="7">
+        <v>241</v>
+      </c>
+      <c r="B1012" s="8" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C1012" s="8" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D1012" s="8"/>
+      <c r="E1012" s="8"/>
+      <c r="F1012" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1012" s="14"/>
+      <c r="H1012" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I1012" s="14"/>
+      <c r="J1012" s="8" t="s">
+        <v>1811</v>
+      </c>
+      <c r="K1012" s="8" t="s">
+        <v>1824</v>
+      </c>
+      <c r="L1012" s="8"/>
+      <c r="M1012" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1012" s="8" t="s">
+        <v>1825</v>
+      </c>
+      <c r="O1012" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1012" s="14"/>
+      <c r="Q1012" s="14"/>
+      <c r="R1012" s="17"/>
+      <c r="S1012" s="17"/>
+      <c r="T1012" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1012" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:21">
+      <c r="A1013" s="7">
+        <v>242</v>
+      </c>
+      <c r="B1013" s="8" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C1013" s="8" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1013" s="8"/>
+      <c r="E1013" s="8"/>
+      <c r="F1013" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1013" s="14"/>
+      <c r="H1013" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I1013" s="14"/>
+      <c r="J1013" s="8" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K1013" s="8" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L1013" s="8"/>
+      <c r="M1013" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1013" s="8" t="s">
+        <v>1829</v>
+      </c>
+      <c r="O1013" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1013" s="14"/>
+      <c r="Q1013" s="14"/>
+      <c r="R1013" s="17"/>
+      <c r="S1013" s="17"/>
+      <c r="T1013" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1013" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:21">
+      <c r="A1014" s="7">
+        <v>243</v>
+      </c>
+      <c r="B1014" s="8" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C1014" s="8" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1014" s="8"/>
+      <c r="E1014" s="8"/>
+      <c r="F1014" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1014" s="14"/>
+      <c r="H1014" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I1014" s="14"/>
+      <c r="J1014" s="8" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K1014" s="8" t="s">
+        <v>1831</v>
+      </c>
+      <c r="L1014" s="8"/>
+      <c r="M1014" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1014" s="8" t="s">
+        <v>1832</v>
+      </c>
+      <c r="O1014" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1014" s="14"/>
+      <c r="Q1014" s="14"/>
+      <c r="R1014" s="17"/>
+      <c r="S1014" s="17"/>
+      <c r="T1014" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1014" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:21">
+      <c r="A1015" s="7">
+        <v>244</v>
+      </c>
+      <c r="B1015" s="8" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C1015" s="8" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D1015" s="8"/>
+      <c r="E1015" s="8"/>
+      <c r="F1015" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1015" s="14"/>
+      <c r="H1015" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I1015" s="14"/>
+      <c r="J1015" s="8" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K1015" s="8" t="s">
+        <v>1834</v>
+      </c>
+      <c r="L1015" s="8"/>
+      <c r="M1015" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1015" s="8" t="s">
+        <v>1836</v>
+      </c>
+      <c r="O1015" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1015" s="14"/>
+      <c r="Q1015" s="14"/>
+      <c r="R1015" s="17"/>
+      <c r="S1015" s="17"/>
+      <c r="T1015" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1015" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:U2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="T5:T1007" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="T5:T1015" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Activo,Inactivo"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="U5:U1007" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="U5:U1015" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -38623,34 +39032,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>1322</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
       <c r="K1" s="33"/>
       <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>1323</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
       <c r="K2" s="34"/>
       <c r="L2" s="34"/>
     </row>
@@ -38682,13 +39091,13 @@
         <v>1327</v>
       </c>
       <c r="E4" s="37"/>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="73" t="s">
         <v>1328</v>
       </c>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
       <c r="K4" s="37"/>
       <c r="L4" s="37"/>
     </row>
@@ -49994,55 +50403,22 @@
       </c>
     </row>
     <row r="252" spans="1:12">
-      <c r="A252" s="55" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B252" s="56">
-        <v>230</v>
-      </c>
-      <c r="C252" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="D252" s="56">
-        <f t="shared" ref="D252" si="45">IF(A252="","",$B$7/$B$6)</f>
-        <v>25</v>
-      </c>
-      <c r="E252" s="58">
-        <f t="shared" ref="E252" si="46">IF(A252="","",IF(C252="NO",0,IF(D252&lt;&gt;"",D252,$B$11)))</f>
-        <v>0</v>
-      </c>
-      <c r="F252" s="58">
-        <f t="shared" ref="F252" si="47">IF(A252="","",$B$7/$B$6)</f>
-        <v>25</v>
-      </c>
-      <c r="G252" s="58">
-        <f t="shared" ref="G252" si="48">IF(A252="","",($B$8-$B$9)/$B$6)</f>
-        <v>0</v>
-      </c>
-      <c r="H252" s="59">
-        <f t="shared" ref="H252" si="49">IF(A252="","",$B$10)</f>
-        <v>0</v>
-      </c>
-      <c r="I252" s="59">
-        <f t="shared" ref="I252" si="50">IF(A252="","",$B$5)</f>
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="J252" s="58">
-        <f t="shared" ref="J252" si="51">IF(OR(A252="",B252=""),"",ROUND((B252+E252+F252+G252)/(1-H252-I252),-1))</f>
-        <v>380</v>
-      </c>
-      <c r="K252" s="58">
-        <f t="shared" ref="K252" si="52">IF(J252="","",J252-B252-E252-F252-G252-(J252*H252))</f>
-        <v>125</v>
-      </c>
-      <c r="L252" s="60">
-        <f t="shared" ref="L252" si="53">IF(J252="","",K252/J252)</f>
-        <v>0.32894736842105265</v>
-      </c>
+      <c r="A252" s="55"/>
+      <c r="B252" s="56"/>
+      <c r="C252" s="57"/>
+      <c r="D252" s="56"/>
+      <c r="E252" s="58"/>
+      <c r="F252" s="58"/>
+      <c r="G252" s="58"/>
+      <c r="H252" s="59"/>
+      <c r="I252" s="59"/>
+      <c r="J252" s="58"/>
+      <c r="K252" s="58"/>
+      <c r="L252" s="60"/>
     </row>
     <row r="253" spans="1:12">
       <c r="A253" s="55" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="B253" s="56">
         <v>230</v>
@@ -50052,135 +50428,391 @@
       </c>
       <c r="D253" s="56"/>
       <c r="E253" s="58">
-        <f t="shared" ref="E253" si="54">IF(A253="","",IF(C253="NO",0,IF(D253&lt;&gt;"",D253,$B$11)))</f>
+        <f t="shared" ref="E253" si="45">IF(A253="","",IF(C253="NO",0,IF(D253&lt;&gt;"",D253,$B$11)))</f>
         <v>1000</v>
       </c>
       <c r="F253" s="58">
-        <f t="shared" ref="F253" si="55">IF(A253="","",$B$7/$B$6)</f>
+        <f t="shared" ref="F253" si="46">IF(A253="","",$B$7/$B$6)</f>
         <v>25</v>
       </c>
       <c r="G253" s="58">
-        <f t="shared" ref="G253" si="56">IF(A253="","",($B$8-$B$9)/$B$6)</f>
+        <f t="shared" ref="G253" si="47">IF(A253="","",($B$8-$B$9)/$B$6)</f>
         <v>0</v>
       </c>
       <c r="H253" s="59">
-        <f t="shared" ref="H253" si="57">IF(A253="","",$B$10)</f>
+        <f t="shared" ref="H253" si="48">IF(A253="","",$B$10)</f>
         <v>0</v>
       </c>
       <c r="I253" s="59">
-        <f t="shared" ref="I253" si="58">IF(A253="","",$B$5)</f>
+        <f t="shared" ref="I253" si="49">IF(A253="","",$B$5)</f>
         <v>0.33300000000000002</v>
       </c>
       <c r="J253" s="58">
-        <f t="shared" ref="J253" si="59">IF(OR(A253="",B253=""),"",ROUND((B253+E253+F253+G253)/(1-H253-I253),-1))</f>
+        <f t="shared" ref="J253" si="50">IF(OR(A253="",B253=""),"",ROUND((B253+E253+F253+G253)/(1-H253-I253),-1))</f>
         <v>1880</v>
       </c>
       <c r="K253" s="58">
-        <f t="shared" ref="K253" si="60">IF(J253="","",J253-B253-E253-F253-G253-(J253*H253))</f>
+        <f t="shared" ref="K253" si="51">IF(J253="","",J253-B253-E253-F253-G253-(J253*H253))</f>
         <v>625</v>
       </c>
       <c r="L253" s="60">
-        <f t="shared" ref="L253" si="61">IF(J253="","",K253/J253)</f>
+        <f t="shared" ref="L253" si="52">IF(J253="","",K253/J253)</f>
         <v>0.33244680851063829</v>
       </c>
     </row>
     <row r="254" spans="1:12">
-      <c r="A254" s="5"/>
-      <c r="B254" s="21"/>
-      <c r="C254" s="22"/>
-      <c r="D254" s="22"/>
-      <c r="E254" s="22"/>
-      <c r="F254" s="25"/>
-      <c r="G254" s="25"/>
-      <c r="H254" s="22"/>
-      <c r="I254" s="22"/>
-      <c r="J254" s="27"/>
+      <c r="A254" s="55" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B254" s="56">
+        <v>19800</v>
+      </c>
+      <c r="C254" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D254" s="56"/>
+      <c r="E254" s="58">
+        <f t="shared" ref="E254" si="53">IF(A254="","",IF(C254="NO",0,IF(D254&lt;&gt;"",D254,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F254" s="58">
+        <f t="shared" ref="F254" si="54">IF(A254="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G254" s="58">
+        <f t="shared" ref="G254" si="55">IF(A254="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H254" s="59">
+        <f t="shared" ref="H254" si="56">IF(A254="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I254" s="59">
+        <f t="shared" ref="I254" si="57">IF(A254="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J254" s="58">
+        <f t="shared" ref="J254" si="58">IF(OR(A254="",B254=""),"",ROUND((B254+E254+F254+G254)/(1-H254-I254),-1))</f>
+        <v>29720</v>
+      </c>
+      <c r="K254" s="58">
+        <f t="shared" ref="K254" si="59">IF(J254="","",J254-B254-E254-F254-G254-(J254*H254))</f>
+        <v>9895</v>
+      </c>
+      <c r="L254" s="60">
+        <f t="shared" ref="L254" si="60">IF(J254="","",K254/J254)</f>
+        <v>0.3329407806191117</v>
+      </c>
     </row>
     <row r="255" spans="1:12">
-      <c r="A255" s="5"/>
-      <c r="B255" s="21"/>
-      <c r="C255" s="22"/>
-      <c r="D255" s="22"/>
-      <c r="E255" s="22"/>
-      <c r="F255" s="25"/>
-      <c r="G255" s="25"/>
-      <c r="H255" s="22"/>
-      <c r="I255" s="22"/>
-      <c r="J255" s="27"/>
+      <c r="A255" s="55" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B255" s="56">
+        <v>10200</v>
+      </c>
+      <c r="C255" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D255" s="56"/>
+      <c r="E255" s="58">
+        <f t="shared" ref="E255" si="61">IF(A255="","",IF(C255="NO",0,IF(D255&lt;&gt;"",D255,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F255" s="58">
+        <f t="shared" ref="F255" si="62">IF(A255="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G255" s="58">
+        <f t="shared" ref="G255" si="63">IF(A255="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H255" s="59">
+        <f t="shared" ref="H255" si="64">IF(A255="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I255" s="59">
+        <f t="shared" ref="I255" si="65">IF(A255="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J255" s="58">
+        <f t="shared" ref="J255" si="66">IF(OR(A255="",B255=""),"",ROUND((B255+E255+F255+G255)/(1-H255-I255),-1))</f>
+        <v>15330</v>
+      </c>
+      <c r="K255" s="58">
+        <f t="shared" ref="K255" si="67">IF(J255="","",J255-B255-E255-F255-G255-(J255*H255))</f>
+        <v>5105</v>
+      </c>
+      <c r="L255" s="60">
+        <f t="shared" ref="L255" si="68">IF(J255="","",K255/J255)</f>
+        <v>0.33300717547292891</v>
+      </c>
     </row>
     <row r="256" spans="1:12">
-      <c r="A256" s="5"/>
-      <c r="B256" s="21"/>
-      <c r="C256" s="22"/>
-      <c r="D256" s="22"/>
-      <c r="E256" s="22"/>
-      <c r="F256" s="25"/>
-      <c r="G256" s="25"/>
-      <c r="H256" s="22"/>
-      <c r="I256" s="22"/>
-      <c r="J256" s="27"/>
-    </row>
-    <row r="257" spans="1:10">
-      <c r="A257" s="5"/>
-      <c r="B257" s="21"/>
-      <c r="C257" s="22"/>
-      <c r="D257" s="22"/>
-      <c r="E257" s="22"/>
-      <c r="F257" s="25"/>
-      <c r="G257" s="25"/>
-      <c r="H257" s="22"/>
-      <c r="I257" s="22"/>
-      <c r="J257" s="27"/>
-    </row>
-    <row r="258" spans="1:10">
-      <c r="A258" s="5"/>
-      <c r="B258" s="21"/>
-      <c r="C258" s="22"/>
-      <c r="D258" s="22"/>
-      <c r="E258" s="22"/>
-      <c r="F258" s="25"/>
-      <c r="G258" s="25"/>
-      <c r="H258" s="22"/>
-      <c r="I258" s="22"/>
-      <c r="J258" s="27"/>
-    </row>
-    <row r="259" spans="1:10">
-      <c r="A259" s="5"/>
-      <c r="B259" s="21"/>
-      <c r="C259" s="22"/>
-      <c r="D259" s="22"/>
-      <c r="E259" s="22"/>
-      <c r="F259" s="25"/>
-      <c r="G259" s="25"/>
-      <c r="H259" s="22"/>
-      <c r="I259" s="22"/>
-      <c r="J259" s="27"/>
-    </row>
-    <row r="260" spans="1:10">
-      <c r="A260" s="5"/>
-      <c r="B260" s="21"/>
-      <c r="C260" s="22"/>
-      <c r="D260" s="22"/>
-      <c r="E260" s="22"/>
-      <c r="F260" s="25"/>
-      <c r="G260" s="25"/>
-      <c r="H260" s="22"/>
-      <c r="I260" s="22"/>
-      <c r="J260" s="27"/>
-    </row>
-    <row r="261" spans="1:10">
-      <c r="A261" s="5"/>
-      <c r="B261" s="21"/>
-      <c r="C261" s="22"/>
-      <c r="D261" s="22"/>
-      <c r="E261" s="22"/>
-      <c r="F261" s="25"/>
-      <c r="G261" s="25"/>
-      <c r="H261" s="22"/>
-      <c r="I261" s="22"/>
-      <c r="J261" s="27"/>
-    </row>
-    <row r="262" spans="1:10">
+      <c r="A256" s="55" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B256" s="56">
+        <v>7100</v>
+      </c>
+      <c r="C256" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D256" s="56"/>
+      <c r="E256" s="58">
+        <f t="shared" ref="E256" si="69">IF(A256="","",IF(C256="NO",0,IF(D256&lt;&gt;"",D256,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F256" s="58">
+        <f t="shared" ref="F256" si="70">IF(A256="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G256" s="58">
+        <f t="shared" ref="G256" si="71">IF(A256="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H256" s="59">
+        <f t="shared" ref="H256" si="72">IF(A256="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I256" s="59">
+        <f t="shared" ref="I256" si="73">IF(A256="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J256" s="58">
+        <f t="shared" ref="J256" si="74">IF(OR(A256="",B256=""),"",ROUND((B256+E256+F256+G256)/(1-H256-I256),-1))</f>
+        <v>10680</v>
+      </c>
+      <c r="K256" s="58">
+        <f t="shared" ref="K256" si="75">IF(J256="","",J256-B256-E256-F256-G256-(J256*H256))</f>
+        <v>3555</v>
+      </c>
+      <c r="L256" s="60">
+        <f t="shared" ref="L256" si="76">IF(J256="","",K256/J256)</f>
+        <v>0.33286516853932585</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12">
+      <c r="A257" s="55" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B257" s="56">
+        <v>17200</v>
+      </c>
+      <c r="C257" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D257" s="56"/>
+      <c r="E257" s="58">
+        <f t="shared" ref="E257" si="77">IF(A257="","",IF(C257="NO",0,IF(D257&lt;&gt;"",D257,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F257" s="58">
+        <f t="shared" ref="F257" si="78">IF(A257="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G257" s="58">
+        <f t="shared" ref="G257" si="79">IF(A257="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H257" s="59">
+        <f t="shared" ref="H257" si="80">IF(A257="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I257" s="59">
+        <f t="shared" ref="I257" si="81">IF(A257="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J257" s="58">
+        <f t="shared" ref="J257" si="82">IF(OR(A257="",B257=""),"",ROUND((B257+E257+F257+G257)/(1-H257-I257),-1))</f>
+        <v>25820</v>
+      </c>
+      <c r="K257" s="58">
+        <f t="shared" ref="K257" si="83">IF(J257="","",J257-B257-E257-F257-G257-(J257*H257))</f>
+        <v>8595</v>
+      </c>
+      <c r="L257" s="60">
+        <f t="shared" ref="L257" si="84">IF(J257="","",K257/J257)</f>
+        <v>0.3328814872192099</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12">
+      <c r="A258" s="55" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B258" s="56">
+        <v>9300</v>
+      </c>
+      <c r="C258" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D258" s="56"/>
+      <c r="E258" s="58">
+        <f t="shared" ref="E258" si="85">IF(A258="","",IF(C258="NO",0,IF(D258&lt;&gt;"",D258,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F258" s="58">
+        <f t="shared" ref="F258" si="86">IF(A258="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G258" s="58">
+        <f t="shared" ref="G258" si="87">IF(A258="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H258" s="59">
+        <f t="shared" ref="H258" si="88">IF(A258="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I258" s="59">
+        <f t="shared" ref="I258" si="89">IF(A258="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J258" s="58">
+        <f t="shared" ref="J258" si="90">IF(OR(A258="",B258=""),"",ROUND((B258+E258+F258+G258)/(1-H258-I258),-1))</f>
+        <v>13980</v>
+      </c>
+      <c r="K258" s="58">
+        <f t="shared" ref="K258" si="91">IF(J258="","",J258-B258-E258-F258-G258-(J258*H258))</f>
+        <v>4655</v>
+      </c>
+      <c r="L258" s="60">
+        <f t="shared" ref="L258" si="92">IF(J258="","",K258/J258)</f>
+        <v>0.33297567954220314</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12">
+      <c r="A259" s="55" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B259" s="56">
+        <v>20000</v>
+      </c>
+      <c r="C259" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D259" s="56"/>
+      <c r="E259" s="58">
+        <f t="shared" ref="E259" si="93">IF(A259="","",IF(C259="NO",0,IF(D259&lt;&gt;"",D259,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F259" s="58">
+        <f t="shared" ref="F259" si="94">IF(A259="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G259" s="58">
+        <f t="shared" ref="G259" si="95">IF(A259="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H259" s="59">
+        <f t="shared" ref="H259" si="96">IF(A259="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I259" s="59">
+        <f t="shared" ref="I259" si="97">IF(A259="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J259" s="58">
+        <f t="shared" ref="J259" si="98">IF(OR(A259="",B259=""),"",ROUND((B259+E259+F259+G259)/(1-H259-I259),-1))</f>
+        <v>30020</v>
+      </c>
+      <c r="K259" s="58">
+        <f t="shared" ref="K259" si="99">IF(J259="","",J259-B259-E259-F259-G259-(J259*H259))</f>
+        <v>9995</v>
+      </c>
+      <c r="L259" s="60">
+        <f t="shared" ref="L259" si="100">IF(J259="","",K259/J259)</f>
+        <v>0.33294470353097932</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12">
+      <c r="A260" s="55" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B260" s="56">
+        <v>15800</v>
+      </c>
+      <c r="C260" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D260" s="56"/>
+      <c r="E260" s="58">
+        <f t="shared" ref="E260" si="101">IF(A260="","",IF(C260="NO",0,IF(D260&lt;&gt;"",D260,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F260" s="58">
+        <f t="shared" ref="F260" si="102">IF(A260="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G260" s="58">
+        <f t="shared" ref="G260" si="103">IF(A260="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H260" s="59">
+        <f t="shared" ref="H260" si="104">IF(A260="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I260" s="59">
+        <f t="shared" ref="I260" si="105">IF(A260="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J260" s="58">
+        <f t="shared" ref="J260" si="106">IF(OR(A260="",B260=""),"",ROUND((B260+E260+F260+G260)/(1-H260-I260),-1))</f>
+        <v>23730</v>
+      </c>
+      <c r="K260" s="58">
+        <f t="shared" ref="K260" si="107">IF(J260="","",J260-B260-E260-F260-G260-(J260*H260))</f>
+        <v>7905</v>
+      </c>
+      <c r="L260" s="60">
+        <f t="shared" ref="L260" si="108">IF(J260="","",K260/J260)</f>
+        <v>0.33312262958280658</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12">
+      <c r="A261" s="55" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B261" s="56">
+        <v>10000</v>
+      </c>
+      <c r="C261" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D261" s="56"/>
+      <c r="E261" s="58">
+        <f t="shared" ref="E261" si="109">IF(A261="","",IF(C261="NO",0,IF(D261&lt;&gt;"",D261,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F261" s="58">
+        <f t="shared" ref="F261" si="110">IF(A261="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G261" s="58">
+        <f t="shared" ref="G261" si="111">IF(A261="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H261" s="59">
+        <f t="shared" ref="H261" si="112">IF(A261="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I261" s="59">
+        <f t="shared" ref="I261" si="113">IF(A261="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J261" s="58">
+        <f t="shared" ref="J261" si="114">IF(OR(A261="",B261=""),"",ROUND((B261+E261+F261+G261)/(1-H261-I261),-1))</f>
+        <v>15030</v>
+      </c>
+      <c r="K261" s="58">
+        <f t="shared" ref="K261" si="115">IF(J261="","",J261-B261-E261-F261-G261-(J261*H261))</f>
+        <v>5005</v>
+      </c>
+      <c r="L261" s="60">
+        <f t="shared" ref="L261" si="116">IF(J261="","",K261/J261)</f>
+        <v>0.33300066533599465</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12">
       <c r="A262" s="5"/>
       <c r="B262" s="21"/>
       <c r="C262" s="22"/>
@@ -50192,7 +50824,7 @@
       <c r="I262" s="22"/>
       <c r="J262" s="27"/>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:12">
       <c r="A263" s="5"/>
       <c r="B263" s="21"/>
       <c r="C263" s="22"/>
@@ -50204,7 +50836,7 @@
       <c r="I263" s="22"/>
       <c r="J263" s="27"/>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" spans="1:12">
       <c r="A264" s="5"/>
       <c r="B264" s="21"/>
       <c r="C264" s="22"/>
@@ -50216,7 +50848,7 @@
       <c r="I264" s="22"/>
       <c r="J264" s="27"/>
     </row>
-    <row r="265" spans="1:10">
+    <row r="265" spans="1:12">
       <c r="A265" s="5"/>
       <c r="B265" s="21"/>
       <c r="C265" s="22"/>
@@ -50228,7 +50860,7 @@
       <c r="I265" s="22"/>
       <c r="J265" s="27"/>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:12">
       <c r="A266" s="5"/>
       <c r="B266" s="21"/>
       <c r="C266" s="22"/>
@@ -50240,7 +50872,7 @@
       <c r="I266" s="22"/>
       <c r="J266" s="27"/>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:12">
       <c r="A267" s="5"/>
       <c r="B267" s="21"/>
       <c r="C267" s="22"/>
@@ -50252,7 +50884,7 @@
       <c r="I267" s="22"/>
       <c r="J267" s="27"/>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:12">
       <c r="A268" s="5"/>
       <c r="B268" s="21"/>
       <c r="C268" s="22"/>
@@ -50264,7 +50896,7 @@
       <c r="I268" s="22"/>
       <c r="J268" s="27"/>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:12">
       <c r="A269" s="5"/>
       <c r="B269" s="21"/>
       <c r="C269" s="22"/>
@@ -50276,7 +50908,7 @@
       <c r="I269" s="22"/>
       <c r="J269" s="27"/>
     </row>
-    <row r="270" spans="1:10">
+    <row r="270" spans="1:12">
       <c r="A270" s="5"/>
       <c r="B270" s="21"/>
       <c r="C270" s="22"/>
@@ -50288,7 +50920,7 @@
       <c r="I270" s="22"/>
       <c r="J270" s="27"/>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:12">
       <c r="A271" s="5"/>
       <c r="B271" s="21"/>
       <c r="C271" s="22"/>
@@ -50300,7 +50932,7 @@
       <c r="I271" s="22"/>
       <c r="J271" s="27"/>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:12">
       <c r="A272" s="5"/>
       <c r="B272" s="21"/>
       <c r="C272" s="22"/>
@@ -59223,7 +59855,7 @@
     <mergeCell ref="F4:J4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C15:C253" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="C15:C261" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"SÍ,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -59257,63 +59889,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>1359</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
     </row>
     <row r="2" spans="1:15" ht="32" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="74" t="s">
         <v>1360</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="74"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="75" t="s">
         <v>1361</v>
       </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="F4" s="74" t="s">
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="F4" s="75" t="s">
         <v>1362</v>
       </c>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="L4" s="74" t="s">
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="L4" s="75" t="s">
         <v>1363</v>
       </c>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
     </row>
     <row r="5" spans="1:15" ht="28">
       <c r="A5" s="2" t="s">
@@ -66398,15 +67030,17 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L233" s="30"/>
+      <c r="L233" s="30" t="s">
+        <v>1321</v>
+      </c>
       <c r="M233" s="6" t="s">
         <v>33</v>
       </c>
       <c r="N233" s="6" t="s">
-        <v>1704</v>
+        <v>1834</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>1370</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="234" spans="6:15">
@@ -67648,7 +68282,7 @@
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="DUPLICADA"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C6:C105 M6:M305 I6:I305" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="C6:C105 I6:I305 M6:M305" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Activo,Inactivo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -67663,12 +68297,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H246"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:8" ht="20">
       <c r="A1" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -67680,33 +68314,33 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="42">
       <c r="A4" s="2" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>1708</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>1709</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>1710</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>1711</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>1712</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -67720,16 +68354,16 @@
         <v>31</v>
       </c>
       <c r="D5" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E5" t="s">
         <v>1714</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>1715</v>
       </c>
-      <c r="F5" t="s">
-        <v>1716</v>
-      </c>
       <c r="G5" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -67737,22 +68371,22 @@
         <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E6" t="s">
         <v>1714</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>1715</v>
       </c>
-      <c r="F6" t="s">
-        <v>1716</v>
-      </c>
       <c r="G6" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -67766,16 +68400,16 @@
         <v>46</v>
       </c>
       <c r="D7" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E7" t="s">
         <v>1714</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>1715</v>
       </c>
-      <c r="F7" t="s">
-        <v>1716</v>
-      </c>
       <c r="G7" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -67789,16 +68423,16 @@
         <v>52</v>
       </c>
       <c r="D8" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E8" t="s">
         <v>1714</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>1715</v>
       </c>
-      <c r="F8" t="s">
-        <v>1716</v>
-      </c>
       <c r="G8" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -67812,16 +68446,16 @@
         <v>60</v>
       </c>
       <c r="D9" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E9" t="s">
         <v>1714</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>1715</v>
       </c>
-      <c r="F9" t="s">
-        <v>1716</v>
-      </c>
       <c r="G9" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -67835,16 +68469,16 @@
         <v>67</v>
       </c>
       <c r="D10" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E10" t="s">
         <v>1714</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>1715</v>
       </c>
-      <c r="F10" t="s">
-        <v>1716</v>
-      </c>
       <c r="G10" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -67858,16 +68492,16 @@
         <v>74</v>
       </c>
       <c r="D11" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E11" t="s">
         <v>1714</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>1715</v>
       </c>
-      <c r="F11" t="s">
-        <v>1716</v>
-      </c>
       <c r="G11" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -67881,16 +68515,16 @@
         <v>83</v>
       </c>
       <c r="D12" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E12" t="s">
         <v>1714</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>1715</v>
       </c>
-      <c r="F12" t="s">
-        <v>1716</v>
-      </c>
       <c r="G12" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -67904,16 +68538,16 @@
         <v>88</v>
       </c>
       <c r="D13" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E13" t="s">
         <v>1714</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>1715</v>
       </c>
-      <c r="F13" t="s">
-        <v>1716</v>
-      </c>
       <c r="G13" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -67927,16 +68561,16 @@
         <v>95</v>
       </c>
       <c r="D14" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E14" t="s">
         <v>1714</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>1715</v>
       </c>
-      <c r="F14" t="s">
-        <v>1716</v>
-      </c>
       <c r="G14" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -67950,16 +68584,16 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E15" t="s">
         <v>1714</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>1715</v>
       </c>
-      <c r="F15" t="s">
-        <v>1716</v>
-      </c>
       <c r="G15" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -67973,16 +68607,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E16" t="s">
         <v>1714</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>1715</v>
       </c>
-      <c r="F16" t="s">
-        <v>1716</v>
-      </c>
       <c r="G16" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -67996,16 +68630,16 @@
         <v>110</v>
       </c>
       <c r="D17" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E17" t="s">
         <v>1714</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>1715</v>
       </c>
-      <c r="F17" t="s">
-        <v>1716</v>
-      </c>
       <c r="G17" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -68019,16 +68653,16 @@
         <v>115</v>
       </c>
       <c r="D18" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E18" t="s">
         <v>1714</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>1715</v>
       </c>
-      <c r="F18" t="s">
-        <v>1716</v>
-      </c>
       <c r="G18" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -68042,16 +68676,16 @@
         <v>123</v>
       </c>
       <c r="D19" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E19" t="s">
         <v>1714</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>1715</v>
       </c>
-      <c r="F19" t="s">
-        <v>1716</v>
-      </c>
       <c r="G19" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -68065,16 +68699,16 @@
         <v>128</v>
       </c>
       <c r="D20" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E20" t="s">
         <v>1714</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>1715</v>
       </c>
-      <c r="F20" t="s">
-        <v>1716</v>
-      </c>
       <c r="G20" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -68088,16 +68722,16 @@
         <v>133</v>
       </c>
       <c r="D21" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E21" t="s">
         <v>1714</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>1715</v>
       </c>
-      <c r="F21" t="s">
-        <v>1716</v>
-      </c>
       <c r="G21" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -68111,16 +68745,16 @@
         <v>140</v>
       </c>
       <c r="D22" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E22" t="s">
         <v>1714</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>1715</v>
       </c>
-      <c r="F22" t="s">
-        <v>1716</v>
-      </c>
       <c r="G22" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -68134,16 +68768,16 @@
         <v>145</v>
       </c>
       <c r="D23" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E23" t="s">
         <v>1714</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>1715</v>
       </c>
-      <c r="F23" t="s">
-        <v>1716</v>
-      </c>
       <c r="G23" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -68157,16 +68791,16 @@
         <v>150</v>
       </c>
       <c r="D24" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E24" t="s">
         <v>1714</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>1715</v>
       </c>
-      <c r="F24" t="s">
-        <v>1716</v>
-      </c>
       <c r="G24" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -68180,16 +68814,16 @@
         <v>154</v>
       </c>
       <c r="D25" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E25" t="s">
         <v>1714</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>1715</v>
       </c>
-      <c r="F25" t="s">
-        <v>1716</v>
-      </c>
       <c r="G25" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -68203,16 +68837,16 @@
         <v>159</v>
       </c>
       <c r="D26" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E26" t="s">
         <v>1714</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>1715</v>
       </c>
-      <c r="F26" t="s">
-        <v>1716</v>
-      </c>
       <c r="G26" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -68226,16 +68860,16 @@
         <v>164</v>
       </c>
       <c r="D27" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E27" t="s">
         <v>1714</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>1715</v>
       </c>
-      <c r="F27" t="s">
-        <v>1716</v>
-      </c>
       <c r="G27" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -68249,16 +68883,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E28" t="s">
         <v>1714</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>1715</v>
       </c>
-      <c r="F28" t="s">
-        <v>1716</v>
-      </c>
       <c r="G28" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -68272,16 +68906,16 @@
         <v>174</v>
       </c>
       <c r="D29" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E29" t="s">
         <v>1714</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>1715</v>
       </c>
-      <c r="F29" t="s">
-        <v>1716</v>
-      </c>
       <c r="G29" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -68295,16 +68929,16 @@
         <v>177</v>
       </c>
       <c r="D30" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E30" t="s">
         <v>1714</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>1715</v>
       </c>
-      <c r="F30" t="s">
-        <v>1716</v>
-      </c>
       <c r="G30" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -68318,16 +68952,16 @@
         <v>181</v>
       </c>
       <c r="D31" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E31" t="s">
         <v>1714</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>1715</v>
       </c>
-      <c r="F31" t="s">
-        <v>1716</v>
-      </c>
       <c r="G31" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -68341,16 +68975,16 @@
         <v>185</v>
       </c>
       <c r="D32" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E32" t="s">
         <v>1714</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>1715</v>
       </c>
-      <c r="F32" t="s">
-        <v>1716</v>
-      </c>
       <c r="G32" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -68364,16 +68998,16 @@
         <v>189</v>
       </c>
       <c r="D33" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E33" t="s">
         <v>1714</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>1715</v>
       </c>
-      <c r="F33" t="s">
-        <v>1716</v>
-      </c>
       <c r="G33" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -68387,16 +69021,16 @@
         <v>195</v>
       </c>
       <c r="D34" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E34" t="s">
         <v>1714</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>1715</v>
       </c>
-      <c r="F34" t="s">
-        <v>1716</v>
-      </c>
       <c r="G34" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -68410,16 +69044,16 @@
         <v>200</v>
       </c>
       <c r="D35" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E35" t="s">
         <v>1714</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>1715</v>
       </c>
-      <c r="F35" t="s">
-        <v>1716</v>
-      </c>
       <c r="G35" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -68433,16 +69067,16 @@
         <v>207</v>
       </c>
       <c r="D36" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E36" t="s">
         <v>1714</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>1715</v>
       </c>
-      <c r="F36" t="s">
-        <v>1716</v>
-      </c>
       <c r="G36" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -68456,16 +69090,16 @@
         <v>212</v>
       </c>
       <c r="D37" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E37" t="s">
         <v>1714</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>1715</v>
       </c>
-      <c r="F37" t="s">
-        <v>1716</v>
-      </c>
       <c r="G37" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -68479,16 +69113,16 @@
         <v>217</v>
       </c>
       <c r="D38" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E38" t="s">
         <v>1714</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>1715</v>
       </c>
-      <c r="F38" t="s">
-        <v>1716</v>
-      </c>
       <c r="G38" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -68502,16 +69136,16 @@
         <v>222</v>
       </c>
       <c r="D39" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E39" t="s">
         <v>1714</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>1715</v>
       </c>
-      <c r="F39" t="s">
-        <v>1716</v>
-      </c>
       <c r="G39" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -68525,16 +69159,16 @@
         <v>229</v>
       </c>
       <c r="D40" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E40" t="s">
         <v>1714</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>1715</v>
       </c>
-      <c r="F40" t="s">
-        <v>1716</v>
-      </c>
       <c r="G40" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -68548,16 +69182,16 @@
         <v>233</v>
       </c>
       <c r="D41" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E41" t="s">
         <v>1714</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>1715</v>
       </c>
-      <c r="F41" t="s">
-        <v>1716</v>
-      </c>
       <c r="G41" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -68571,16 +69205,16 @@
         <v>241</v>
       </c>
       <c r="D42" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E42" t="s">
         <v>1714</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>1715</v>
       </c>
-      <c r="F42" t="s">
-        <v>1716</v>
-      </c>
       <c r="G42" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -68594,16 +69228,16 @@
         <v>247</v>
       </c>
       <c r="D43" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E43" t="s">
         <v>1714</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>1715</v>
       </c>
-      <c r="F43" t="s">
-        <v>1716</v>
-      </c>
       <c r="G43" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -68617,16 +69251,16 @@
         <v>253</v>
       </c>
       <c r="D44" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E44" t="s">
         <v>1714</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>1715</v>
       </c>
-      <c r="F44" t="s">
-        <v>1716</v>
-      </c>
       <c r="G44" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -68640,16 +69274,16 @@
         <v>259</v>
       </c>
       <c r="D45" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E45" t="s">
         <v>1714</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>1715</v>
       </c>
-      <c r="F45" t="s">
-        <v>1716</v>
-      </c>
       <c r="G45" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -68663,16 +69297,16 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E46" t="s">
         <v>1714</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>1715</v>
       </c>
-      <c r="F46" t="s">
-        <v>1716</v>
-      </c>
       <c r="G46" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -68686,16 +69320,16 @@
         <v>269</v>
       </c>
       <c r="D47" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E47" t="s">
         <v>1714</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>1715</v>
       </c>
-      <c r="F47" t="s">
-        <v>1716</v>
-      </c>
       <c r="G47" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -68709,16 +69343,16 @@
         <v>276</v>
       </c>
       <c r="D48" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E48" t="s">
         <v>1714</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>1715</v>
       </c>
-      <c r="F48" t="s">
-        <v>1716</v>
-      </c>
       <c r="G48" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -68732,16 +69366,16 @@
         <v>281</v>
       </c>
       <c r="D49" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E49" t="s">
         <v>1714</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>1715</v>
       </c>
-      <c r="F49" t="s">
-        <v>1716</v>
-      </c>
       <c r="G49" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -68755,16 +69389,16 @@
         <v>286</v>
       </c>
       <c r="D50" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E50" t="s">
         <v>1714</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>1715</v>
       </c>
-      <c r="F50" t="s">
-        <v>1716</v>
-      </c>
       <c r="G50" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -68778,16 +69412,16 @@
         <v>291</v>
       </c>
       <c r="D51" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E51" t="s">
         <v>1714</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>1715</v>
       </c>
-      <c r="F51" t="s">
-        <v>1716</v>
-      </c>
       <c r="G51" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -68801,16 +69435,16 @@
         <v>296</v>
       </c>
       <c r="D52" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E52" t="s">
         <v>1714</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>1715</v>
       </c>
-      <c r="F52" t="s">
-        <v>1716</v>
-      </c>
       <c r="G52" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -68824,16 +69458,16 @@
         <v>301</v>
       </c>
       <c r="D53" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E53" t="s">
         <v>1714</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>1715</v>
       </c>
-      <c r="F53" t="s">
-        <v>1716</v>
-      </c>
       <c r="G53" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -68847,16 +69481,16 @@
         <v>306</v>
       </c>
       <c r="D54" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E54" t="s">
         <v>1714</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>1715</v>
       </c>
-      <c r="F54" t="s">
-        <v>1716</v>
-      </c>
       <c r="G54" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -68870,16 +69504,16 @@
         <v>311</v>
       </c>
       <c r="D55" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E55" t="s">
         <v>1714</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>1715</v>
       </c>
-      <c r="F55" t="s">
-        <v>1716</v>
-      </c>
       <c r="G55" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -68893,16 +69527,16 @@
         <v>316</v>
       </c>
       <c r="D56" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E56" t="s">
         <v>1714</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>1715</v>
       </c>
-      <c r="F56" t="s">
-        <v>1716</v>
-      </c>
       <c r="G56" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -68916,16 +69550,16 @@
         <v>321</v>
       </c>
       <c r="D57" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E57" t="s">
         <v>1714</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>1715</v>
       </c>
-      <c r="F57" t="s">
-        <v>1716</v>
-      </c>
       <c r="G57" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -68939,16 +69573,16 @@
         <v>326</v>
       </c>
       <c r="D58" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E58" t="s">
         <v>1714</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>1715</v>
       </c>
-      <c r="F58" t="s">
-        <v>1716</v>
-      </c>
       <c r="G58" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -68962,16 +69596,16 @@
         <v>331</v>
       </c>
       <c r="D59" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E59" t="s">
         <v>1714</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>1715</v>
       </c>
-      <c r="F59" t="s">
-        <v>1716</v>
-      </c>
       <c r="G59" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -68985,16 +69619,16 @@
         <v>337</v>
       </c>
       <c r="D60" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E60" t="s">
         <v>1714</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>1715</v>
       </c>
-      <c r="F60" t="s">
-        <v>1716</v>
-      </c>
       <c r="G60" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -69008,16 +69642,16 @@
         <v>342</v>
       </c>
       <c r="D61" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E61" t="s">
         <v>1714</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>1715</v>
       </c>
-      <c r="F61" t="s">
-        <v>1716</v>
-      </c>
       <c r="G61" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -69031,16 +69665,16 @@
         <v>347</v>
       </c>
       <c r="D62" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E62" t="s">
         <v>1714</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>1715</v>
       </c>
-      <c r="F62" t="s">
-        <v>1716</v>
-      </c>
       <c r="G62" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -69054,16 +69688,16 @@
         <v>352</v>
       </c>
       <c r="D63" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E63" t="s">
         <v>1714</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>1715</v>
       </c>
-      <c r="F63" t="s">
-        <v>1716</v>
-      </c>
       <c r="G63" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -69077,16 +69711,16 @@
         <v>357</v>
       </c>
       <c r="D64" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E64" t="s">
         <v>1714</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>1715</v>
       </c>
-      <c r="F64" t="s">
-        <v>1716</v>
-      </c>
       <c r="G64" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -69100,16 +69734,16 @@
         <v>362</v>
       </c>
       <c r="D65" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E65" t="s">
         <v>1714</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>1715</v>
       </c>
-      <c r="F65" t="s">
-        <v>1716</v>
-      </c>
       <c r="G65" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -69123,16 +69757,16 @@
         <v>367</v>
       </c>
       <c r="D66" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E66" t="s">
         <v>1714</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>1715</v>
       </c>
-      <c r="F66" t="s">
-        <v>1716</v>
-      </c>
       <c r="G66" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -69146,16 +69780,16 @@
         <v>372</v>
       </c>
       <c r="D67" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E67" t="s">
         <v>1714</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>1715</v>
       </c>
-      <c r="F67" t="s">
-        <v>1716</v>
-      </c>
       <c r="G67" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -69169,16 +69803,16 @@
         <v>377</v>
       </c>
       <c r="D68" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E68" t="s">
         <v>1714</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>1715</v>
       </c>
-      <c r="F68" t="s">
-        <v>1716</v>
-      </c>
       <c r="G68" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -69192,16 +69826,16 @@
         <v>382</v>
       </c>
       <c r="D69" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E69" t="s">
         <v>1714</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>1715</v>
       </c>
-      <c r="F69" t="s">
-        <v>1716</v>
-      </c>
       <c r="G69" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -69215,16 +69849,16 @@
         <v>387</v>
       </c>
       <c r="D70" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E70" t="s">
         <v>1714</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>1715</v>
       </c>
-      <c r="F70" t="s">
-        <v>1716</v>
-      </c>
       <c r="G70" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -69238,16 +69872,16 @@
         <v>392</v>
       </c>
       <c r="D71" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E71" t="s">
         <v>1714</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>1715</v>
       </c>
-      <c r="F71" t="s">
-        <v>1716</v>
-      </c>
       <c r="G71" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -69261,16 +69895,16 @@
         <v>397</v>
       </c>
       <c r="D72" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E72" t="s">
         <v>1714</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>1715</v>
       </c>
-      <c r="F72" t="s">
-        <v>1716</v>
-      </c>
       <c r="G72" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -69284,16 +69918,16 @@
         <v>402</v>
       </c>
       <c r="D73" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E73" t="s">
         <v>1714</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>1715</v>
       </c>
-      <c r="F73" t="s">
-        <v>1716</v>
-      </c>
       <c r="G73" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -69307,16 +69941,16 @@
         <v>407</v>
       </c>
       <c r="D74" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E74" t="s">
         <v>1714</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>1715</v>
       </c>
-      <c r="F74" t="s">
-        <v>1716</v>
-      </c>
       <c r="G74" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -69330,16 +69964,16 @@
         <v>412</v>
       </c>
       <c r="D75" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E75" t="s">
         <v>1714</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>1715</v>
       </c>
-      <c r="F75" t="s">
-        <v>1716</v>
-      </c>
       <c r="G75" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -69353,16 +69987,16 @@
         <v>416</v>
       </c>
       <c r="D76" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E76" t="s">
         <v>1714</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>1715</v>
       </c>
-      <c r="F76" t="s">
-        <v>1716</v>
-      </c>
       <c r="G76" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -69376,16 +70010,16 @@
         <v>419</v>
       </c>
       <c r="D77" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E77" t="s">
         <v>1714</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>1715</v>
       </c>
-      <c r="F77" t="s">
-        <v>1716</v>
-      </c>
       <c r="G77" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -69399,16 +70033,16 @@
         <v>422</v>
       </c>
       <c r="D78" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E78" t="s">
         <v>1714</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>1715</v>
       </c>
-      <c r="F78" t="s">
-        <v>1716</v>
-      </c>
       <c r="G78" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -69422,16 +70056,16 @@
         <v>426</v>
       </c>
       <c r="D79" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E79" t="s">
         <v>1714</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>1715</v>
       </c>
-      <c r="F79" t="s">
-        <v>1716</v>
-      </c>
       <c r="G79" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -69445,16 +70079,16 @@
         <v>433</v>
       </c>
       <c r="D80" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E80" t="s">
         <v>1714</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>1715</v>
       </c>
-      <c r="F80" t="s">
-        <v>1716</v>
-      </c>
       <c r="G80" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -69468,16 +70102,16 @@
         <v>439</v>
       </c>
       <c r="D81" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E81" t="s">
         <v>1714</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>1715</v>
       </c>
-      <c r="F81" t="s">
-        <v>1716</v>
-      </c>
       <c r="G81" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -69491,16 +70125,16 @@
         <v>445</v>
       </c>
       <c r="D82" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E82" t="s">
         <v>1714</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>1715</v>
       </c>
-      <c r="F82" t="s">
-        <v>1716</v>
-      </c>
       <c r="G82" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -69514,16 +70148,16 @@
         <v>454</v>
       </c>
       <c r="D83" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E83" t="s">
         <v>1714</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>1715</v>
       </c>
-      <c r="F83" t="s">
-        <v>1716</v>
-      </c>
       <c r="G83" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -69537,16 +70171,16 @@
         <v>459</v>
       </c>
       <c r="D84" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E84" t="s">
         <v>1714</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>1715</v>
       </c>
-      <c r="F84" t="s">
-        <v>1716</v>
-      </c>
       <c r="G84" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -69560,16 +70194,16 @@
         <v>464</v>
       </c>
       <c r="D85" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E85" t="s">
         <v>1714</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>1715</v>
       </c>
-      <c r="F85" t="s">
-        <v>1716</v>
-      </c>
       <c r="G85" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -69583,16 +70217,16 @@
         <v>469</v>
       </c>
       <c r="D86" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E86" t="s">
         <v>1714</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>1715</v>
       </c>
-      <c r="F86" t="s">
-        <v>1716</v>
-      </c>
       <c r="G86" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -69606,16 +70240,16 @@
         <v>474</v>
       </c>
       <c r="D87" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E87" t="s">
         <v>1714</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>1715</v>
       </c>
-      <c r="F87" t="s">
-        <v>1716</v>
-      </c>
       <c r="G87" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -69629,16 +70263,16 @@
         <v>479</v>
       </c>
       <c r="D88" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E88" t="s">
         <v>1714</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>1715</v>
       </c>
-      <c r="F88" t="s">
-        <v>1716</v>
-      </c>
       <c r="G88" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -69652,16 +70286,16 @@
         <v>484</v>
       </c>
       <c r="D89" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E89" t="s">
         <v>1714</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>1715</v>
       </c>
-      <c r="F89" t="s">
-        <v>1716</v>
-      </c>
       <c r="G89" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -69675,16 +70309,16 @@
         <v>489</v>
       </c>
       <c r="D90" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E90" t="s">
         <v>1714</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>1715</v>
       </c>
-      <c r="F90" t="s">
-        <v>1716</v>
-      </c>
       <c r="G90" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -69698,16 +70332,16 @@
         <v>494</v>
       </c>
       <c r="D91" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E91" t="s">
         <v>1714</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>1715</v>
       </c>
-      <c r="F91" t="s">
-        <v>1716</v>
-      </c>
       <c r="G91" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -69721,16 +70355,16 @@
         <v>500</v>
       </c>
       <c r="D92" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E92" t="s">
         <v>1714</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>1715</v>
       </c>
-      <c r="F92" t="s">
-        <v>1716</v>
-      </c>
       <c r="G92" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -69744,16 +70378,16 @@
         <v>507</v>
       </c>
       <c r="D93" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E93" t="s">
         <v>1714</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>1715</v>
       </c>
-      <c r="F93" t="s">
-        <v>1716</v>
-      </c>
       <c r="G93" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -69767,16 +70401,16 @@
         <v>514</v>
       </c>
       <c r="D94" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E94" t="s">
         <v>1714</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>1715</v>
       </c>
-      <c r="F94" t="s">
-        <v>1716</v>
-      </c>
       <c r="G94" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -69790,16 +70424,16 @@
         <v>518</v>
       </c>
       <c r="D95" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E95" t="s">
         <v>1714</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>1715</v>
       </c>
-      <c r="F95" t="s">
-        <v>1716</v>
-      </c>
       <c r="G95" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -69813,16 +70447,16 @@
         <v>523</v>
       </c>
       <c r="D96" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E96" t="s">
         <v>1714</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>1715</v>
       </c>
-      <c r="F96" t="s">
-        <v>1716</v>
-      </c>
       <c r="G96" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -69836,16 +70470,16 @@
         <v>527</v>
       </c>
       <c r="D97" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E97" t="s">
         <v>1714</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>1715</v>
       </c>
-      <c r="F97" t="s">
-        <v>1716</v>
-      </c>
       <c r="G97" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -69859,16 +70493,16 @@
         <v>532</v>
       </c>
       <c r="D98" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E98" t="s">
         <v>1714</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>1715</v>
       </c>
-      <c r="F98" t="s">
-        <v>1716</v>
-      </c>
       <c r="G98" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -69882,16 +70516,16 @@
         <v>538</v>
       </c>
       <c r="D99" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E99" t="s">
         <v>1714</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>1715</v>
       </c>
-      <c r="F99" t="s">
-        <v>1716</v>
-      </c>
       <c r="G99" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -69905,16 +70539,16 @@
         <v>544</v>
       </c>
       <c r="D100" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E100" t="s">
         <v>1714</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>1715</v>
       </c>
-      <c r="F100" t="s">
-        <v>1716</v>
-      </c>
       <c r="G100" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -69928,16 +70562,16 @@
         <v>550</v>
       </c>
       <c r="D101" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E101" t="s">
         <v>1714</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>1715</v>
       </c>
-      <c r="F101" t="s">
-        <v>1716</v>
-      </c>
       <c r="G101" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -69951,16 +70585,16 @@
         <v>556</v>
       </c>
       <c r="D102" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E102" t="s">
         <v>1714</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>1715</v>
       </c>
-      <c r="F102" t="s">
-        <v>1716</v>
-      </c>
       <c r="G102" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -69974,16 +70608,16 @@
         <v>561</v>
       </c>
       <c r="D103" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E103" t="s">
         <v>1714</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>1715</v>
       </c>
-      <c r="F103" t="s">
-        <v>1716</v>
-      </c>
       <c r="G103" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -69997,16 +70631,16 @@
         <v>566</v>
       </c>
       <c r="D104" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E104" t="s">
         <v>1714</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>1715</v>
       </c>
-      <c r="F104" t="s">
-        <v>1716</v>
-      </c>
       <c r="G104" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -70020,16 +70654,16 @@
         <v>571</v>
       </c>
       <c r="D105" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E105" t="s">
         <v>1714</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>1715</v>
       </c>
-      <c r="F105" t="s">
-        <v>1716</v>
-      </c>
       <c r="G105" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -70043,16 +70677,16 @@
         <v>576</v>
       </c>
       <c r="D106" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E106" t="s">
         <v>1714</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>1715</v>
       </c>
-      <c r="F106" t="s">
-        <v>1716</v>
-      </c>
       <c r="G106" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -70066,16 +70700,16 @@
         <v>585</v>
       </c>
       <c r="D107" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E107" t="s">
         <v>1714</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>1715</v>
       </c>
-      <c r="F107" t="s">
-        <v>1716</v>
-      </c>
       <c r="G107" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -70089,16 +70723,16 @@
         <v>590</v>
       </c>
       <c r="D108" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E108" t="s">
         <v>1714</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>1715</v>
       </c>
-      <c r="F108" t="s">
-        <v>1716</v>
-      </c>
       <c r="G108" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -70112,16 +70746,16 @@
         <v>594</v>
       </c>
       <c r="D109" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E109" t="s">
         <v>1714</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>1715</v>
       </c>
-      <c r="F109" t="s">
-        <v>1716</v>
-      </c>
       <c r="G109" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -70135,16 +70769,16 @@
         <v>599</v>
       </c>
       <c r="D110" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E110" t="s">
         <v>1714</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>1715</v>
       </c>
-      <c r="F110" t="s">
-        <v>1716</v>
-      </c>
       <c r="G110" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -70158,16 +70792,16 @@
         <v>603</v>
       </c>
       <c r="D111" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E111" t="s">
         <v>1714</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>1715</v>
       </c>
-      <c r="F111" t="s">
-        <v>1716</v>
-      </c>
       <c r="G111" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -70181,16 +70815,16 @@
         <v>608</v>
       </c>
       <c r="D112" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E112" t="s">
         <v>1714</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>1715</v>
       </c>
-      <c r="F112" t="s">
-        <v>1716</v>
-      </c>
       <c r="G112" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -70204,16 +70838,16 @@
         <v>613</v>
       </c>
       <c r="D113" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E113" t="s">
         <v>1714</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>1715</v>
       </c>
-      <c r="F113" t="s">
-        <v>1716</v>
-      </c>
       <c r="G113" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -70227,16 +70861,16 @@
         <v>618</v>
       </c>
       <c r="D114" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E114" t="s">
         <v>1714</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>1715</v>
       </c>
-      <c r="F114" t="s">
-        <v>1716</v>
-      </c>
       <c r="G114" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -70250,16 +70884,16 @@
         <v>623</v>
       </c>
       <c r="D115" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E115" t="s">
         <v>1714</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>1715</v>
       </c>
-      <c r="F115" t="s">
-        <v>1716</v>
-      </c>
       <c r="G115" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -70273,16 +70907,16 @@
         <v>628</v>
       </c>
       <c r="D116" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E116" t="s">
         <v>1714</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>1715</v>
       </c>
-      <c r="F116" t="s">
-        <v>1716</v>
-      </c>
       <c r="G116" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -70296,16 +70930,16 @@
         <v>633</v>
       </c>
       <c r="D117" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E117" t="s">
         <v>1714</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>1715</v>
       </c>
-      <c r="F117" t="s">
-        <v>1716</v>
-      </c>
       <c r="G117" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -70319,16 +70953,16 @@
         <v>638</v>
       </c>
       <c r="D118" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E118" t="s">
         <v>1714</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>1715</v>
       </c>
-      <c r="F118" t="s">
-        <v>1716</v>
-      </c>
       <c r="G118" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -70342,16 +70976,16 @@
         <v>643</v>
       </c>
       <c r="D119" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E119" t="s">
         <v>1714</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>1715</v>
       </c>
-      <c r="F119" t="s">
-        <v>1716</v>
-      </c>
       <c r="G119" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -70365,16 +70999,16 @@
         <v>648</v>
       </c>
       <c r="D120" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E120" t="s">
         <v>1714</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>1715</v>
       </c>
-      <c r="F120" t="s">
-        <v>1716</v>
-      </c>
       <c r="G120" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -70388,16 +71022,16 @@
         <v>653</v>
       </c>
       <c r="D121" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E121" t="s">
         <v>1714</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
         <v>1715</v>
       </c>
-      <c r="F121" t="s">
-        <v>1716</v>
-      </c>
       <c r="G121" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -70411,16 +71045,16 @@
         <v>657</v>
       </c>
       <c r="D122" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E122" t="s">
         <v>1714</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>1715</v>
       </c>
-      <c r="F122" t="s">
-        <v>1716</v>
-      </c>
       <c r="G122" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -70434,16 +71068,16 @@
         <v>661</v>
       </c>
       <c r="D123" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E123" t="s">
         <v>1714</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>1715</v>
       </c>
-      <c r="F123" t="s">
-        <v>1716</v>
-      </c>
       <c r="G123" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -70457,16 +71091,16 @@
         <v>666</v>
       </c>
       <c r="D124" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E124" t="s">
         <v>1714</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>1715</v>
       </c>
-      <c r="F124" t="s">
-        <v>1716</v>
-      </c>
       <c r="G124" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -70480,16 +71114,16 @@
         <v>671</v>
       </c>
       <c r="D125" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E125" t="s">
         <v>1714</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>1715</v>
       </c>
-      <c r="F125" t="s">
-        <v>1716</v>
-      </c>
       <c r="G125" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -70503,16 +71137,16 @@
         <v>676</v>
       </c>
       <c r="D126" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E126" t="s">
         <v>1714</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>1715</v>
       </c>
-      <c r="F126" t="s">
-        <v>1716</v>
-      </c>
       <c r="G126" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -70526,16 +71160,16 @@
         <v>680</v>
       </c>
       <c r="D127" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E127" t="s">
         <v>1714</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>1715</v>
       </c>
-      <c r="F127" t="s">
-        <v>1716</v>
-      </c>
       <c r="G127" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -70549,16 +71183,16 @@
         <v>685</v>
       </c>
       <c r="D128" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E128" t="s">
         <v>1714</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>1715</v>
       </c>
-      <c r="F128" t="s">
-        <v>1716</v>
-      </c>
       <c r="G128" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -70572,16 +71206,16 @@
         <v>692</v>
       </c>
       <c r="D129" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E129" t="s">
         <v>1714</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>1715</v>
       </c>
-      <c r="F129" t="s">
-        <v>1716</v>
-      </c>
       <c r="G129" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -70595,16 +71229,16 @@
         <v>697</v>
       </c>
       <c r="D130" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E130" t="s">
         <v>1714</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>1715</v>
       </c>
-      <c r="F130" t="s">
-        <v>1716</v>
-      </c>
       <c r="G130" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -70618,16 +71252,16 @@
         <v>702</v>
       </c>
       <c r="D131" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E131" t="s">
         <v>1714</v>
       </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
         <v>1715</v>
       </c>
-      <c r="F131" t="s">
-        <v>1716</v>
-      </c>
       <c r="G131" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -70641,16 +71275,16 @@
         <v>707</v>
       </c>
       <c r="D132" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E132" t="s">
         <v>1714</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>1715</v>
       </c>
-      <c r="F132" t="s">
-        <v>1716</v>
-      </c>
       <c r="G132" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -70664,16 +71298,16 @@
         <v>712</v>
       </c>
       <c r="D133" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E133" t="s">
         <v>1714</v>
       </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
         <v>1715</v>
       </c>
-      <c r="F133" t="s">
-        <v>1716</v>
-      </c>
       <c r="G133" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -70687,16 +71321,16 @@
         <v>719</v>
       </c>
       <c r="D134" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E134" t="s">
         <v>1718</v>
       </c>
-      <c r="E134" t="s">
+      <c r="F134" t="s">
         <v>1719</v>
       </c>
-      <c r="F134" t="s">
-        <v>1720</v>
-      </c>
       <c r="G134" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -70710,16 +71344,16 @@
         <v>725</v>
       </c>
       <c r="D135" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E135" t="s">
         <v>1718</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
         <v>1719</v>
       </c>
-      <c r="F135" t="s">
-        <v>1720</v>
-      </c>
       <c r="G135" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -70733,16 +71367,16 @@
         <v>731</v>
       </c>
       <c r="D136" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E136" t="s">
         <v>1718</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>1719</v>
       </c>
-      <c r="F136" t="s">
-        <v>1720</v>
-      </c>
       <c r="G136" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -70756,16 +71390,16 @@
         <v>738</v>
       </c>
       <c r="D137" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E137" t="s">
         <v>1714</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
         <v>1715</v>
       </c>
-      <c r="F137" t="s">
-        <v>1716</v>
-      </c>
       <c r="G137" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -70779,16 +71413,16 @@
         <v>745</v>
       </c>
       <c r="D138" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E138" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F138" t="s">
         <v>1721</v>
       </c>
-      <c r="F138" t="s">
-        <v>1722</v>
-      </c>
       <c r="G138" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -70796,22 +71430,22 @@
         <v>748</v>
       </c>
       <c r="B139" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="C139" t="s">
         <v>750</v>
       </c>
       <c r="D139" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E139" t="s">
         <v>1714</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>1715</v>
       </c>
-      <c r="F139" t="s">
-        <v>1716</v>
-      </c>
       <c r="G139" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -70825,16 +71459,16 @@
         <v>755</v>
       </c>
       <c r="D140" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E140" t="s">
         <v>1714</v>
       </c>
-      <c r="E140" t="s">
+      <c r="F140" t="s">
         <v>1715</v>
       </c>
-      <c r="F140" t="s">
-        <v>1716</v>
-      </c>
       <c r="G140" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -70848,16 +71482,16 @@
         <v>761</v>
       </c>
       <c r="D141" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E141" t="s">
         <v>1714</v>
       </c>
-      <c r="E141" t="s">
+      <c r="F141" t="s">
         <v>1715</v>
       </c>
-      <c r="F141" t="s">
-        <v>1716</v>
-      </c>
       <c r="G141" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -70871,16 +71505,16 @@
         <v>766</v>
       </c>
       <c r="D142" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E142" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F142" t="s">
         <v>1721</v>
       </c>
-      <c r="F142" t="s">
-        <v>1722</v>
-      </c>
       <c r="G142" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -70894,16 +71528,16 @@
         <v>772</v>
       </c>
       <c r="D143" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E143" t="s">
         <v>1714</v>
       </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>1715</v>
       </c>
-      <c r="F143" t="s">
-        <v>1716</v>
-      </c>
       <c r="G143" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -70917,16 +71551,16 @@
         <v>777</v>
       </c>
       <c r="D144" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E144" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F144" t="s">
         <v>1721</v>
       </c>
-      <c r="F144" t="s">
-        <v>1722</v>
-      </c>
       <c r="G144" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -70940,16 +71574,16 @@
         <v>782</v>
       </c>
       <c r="D145" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E145" t="s">
         <v>1714</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
         <v>1715</v>
       </c>
-      <c r="F145" t="s">
-        <v>1716</v>
-      </c>
       <c r="G145" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -70963,16 +71597,16 @@
         <v>787</v>
       </c>
       <c r="D146" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E146" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F146" t="s">
         <v>1721</v>
       </c>
-      <c r="F146" t="s">
-        <v>1722</v>
-      </c>
       <c r="G146" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -70986,16 +71620,16 @@
         <v>792</v>
       </c>
       <c r="D147" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E147" t="s">
         <v>1714</v>
       </c>
-      <c r="E147" t="s">
+      <c r="F147" t="s">
         <v>1715</v>
       </c>
-      <c r="F147" t="s">
-        <v>1716</v>
-      </c>
       <c r="G147" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -71009,16 +71643,16 @@
         <v>797</v>
       </c>
       <c r="D148" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E148" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F148" t="s">
         <v>1721</v>
       </c>
-      <c r="F148" t="s">
-        <v>1722</v>
-      </c>
       <c r="G148" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -71032,16 +71666,16 @@
         <v>806</v>
       </c>
       <c r="D149" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E149" t="s">
         <v>1714</v>
       </c>
-      <c r="E149" t="s">
+      <c r="F149" t="s">
         <v>1715</v>
       </c>
-      <c r="F149" t="s">
-        <v>1716</v>
-      </c>
       <c r="G149" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -71055,16 +71689,16 @@
         <v>812</v>
       </c>
       <c r="D150" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E150" t="s">
         <v>1714</v>
       </c>
-      <c r="E150" t="s">
+      <c r="F150" t="s">
         <v>1715</v>
       </c>
-      <c r="F150" t="s">
-        <v>1716</v>
-      </c>
       <c r="G150" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -71078,16 +71712,16 @@
         <v>819</v>
       </c>
       <c r="D151" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E151" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F151" t="s">
         <v>1721</v>
       </c>
-      <c r="F151" t="s">
-        <v>1722</v>
-      </c>
       <c r="G151" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -71101,16 +71735,16 @@
         <v>825</v>
       </c>
       <c r="D152" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E152" t="s">
         <v>1714</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
         <v>1715</v>
       </c>
-      <c r="F152" t="s">
-        <v>1716</v>
-      </c>
       <c r="G152" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -71124,16 +71758,16 @@
         <v>829</v>
       </c>
       <c r="D153" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E153" t="s">
         <v>1714</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
         <v>1715</v>
       </c>
-      <c r="F153" t="s">
-        <v>1716</v>
-      </c>
       <c r="G153" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -71147,16 +71781,16 @@
         <v>833</v>
       </c>
       <c r="D154" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E154" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F154" t="s">
         <v>1721</v>
       </c>
-      <c r="F154" t="s">
-        <v>1722</v>
-      </c>
       <c r="G154" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -71170,16 +71804,16 @@
         <v>839</v>
       </c>
       <c r="D155" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E155" t="s">
         <v>1714</v>
       </c>
-      <c r="E155" t="s">
+      <c r="F155" t="s">
         <v>1715</v>
       </c>
-      <c r="F155" t="s">
-        <v>1716</v>
-      </c>
       <c r="G155" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -71193,16 +71827,16 @@
         <v>843</v>
       </c>
       <c r="D156" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E156" t="s">
         <v>1714</v>
       </c>
-      <c r="E156" t="s">
+      <c r="F156" t="s">
         <v>1715</v>
       </c>
-      <c r="F156" t="s">
-        <v>1716</v>
-      </c>
       <c r="G156" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -71216,16 +71850,16 @@
         <v>847</v>
       </c>
       <c r="D157" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E157" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F157" t="s">
         <v>1721</v>
       </c>
-      <c r="F157" t="s">
-        <v>1722</v>
-      </c>
       <c r="G157" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -71239,16 +71873,16 @@
         <v>852</v>
       </c>
       <c r="D158" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E158" t="s">
         <v>1714</v>
       </c>
-      <c r="E158" t="s">
+      <c r="F158" t="s">
         <v>1715</v>
       </c>
-      <c r="F158" t="s">
-        <v>1716</v>
-      </c>
       <c r="G158" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -71262,16 +71896,16 @@
         <v>856</v>
       </c>
       <c r="D159" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E159" t="s">
         <v>1714</v>
       </c>
-      <c r="E159" t="s">
+      <c r="F159" t="s">
         <v>1715</v>
       </c>
-      <c r="F159" t="s">
-        <v>1716</v>
-      </c>
       <c r="G159" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -71285,16 +71919,16 @@
         <v>860</v>
       </c>
       <c r="D160" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E160" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F160" t="s">
         <v>1721</v>
       </c>
-      <c r="F160" t="s">
-        <v>1722</v>
-      </c>
       <c r="G160" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -71308,16 +71942,16 @@
         <v>869</v>
       </c>
       <c r="D161" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E161" t="s">
         <v>1714</v>
       </c>
-      <c r="E161" t="s">
+      <c r="F161" t="s">
         <v>1715</v>
       </c>
-      <c r="F161" t="s">
-        <v>1716</v>
-      </c>
       <c r="G161" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -71331,16 +71965,16 @@
         <v>876</v>
       </c>
       <c r="D162" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E162" t="s">
         <v>1714</v>
       </c>
-      <c r="E162" t="s">
+      <c r="F162" t="s">
         <v>1715</v>
       </c>
-      <c r="F162" t="s">
-        <v>1716</v>
-      </c>
       <c r="G162" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -71354,16 +71988,16 @@
         <v>883</v>
       </c>
       <c r="D163" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E163" t="s">
         <v>1714</v>
       </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
         <v>1715</v>
       </c>
-      <c r="F163" t="s">
-        <v>1716</v>
-      </c>
       <c r="G163" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -71377,16 +72011,16 @@
         <v>888</v>
       </c>
       <c r="D164" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E164" t="s">
         <v>1714</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
         <v>1715</v>
       </c>
-      <c r="F164" t="s">
-        <v>1716</v>
-      </c>
       <c r="G164" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -71400,16 +72034,16 @@
         <v>893</v>
       </c>
       <c r="D165" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E165" t="s">
         <v>1714</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
         <v>1715</v>
       </c>
-      <c r="F165" t="s">
-        <v>1716</v>
-      </c>
       <c r="G165" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -71423,16 +72057,16 @@
         <v>898</v>
       </c>
       <c r="D166" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E166" t="s">
         <v>1714</v>
       </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
         <v>1715</v>
       </c>
-      <c r="F166" t="s">
-        <v>1716</v>
-      </c>
       <c r="G166" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -71446,16 +72080,16 @@
         <v>903</v>
       </c>
       <c r="D167" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E167" t="s">
         <v>1714</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
         <v>1715</v>
       </c>
-      <c r="F167" t="s">
-        <v>1716</v>
-      </c>
       <c r="G167" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -71469,16 +72103,16 @@
         <v>910</v>
       </c>
       <c r="D168" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E168" t="s">
         <v>1714</v>
       </c>
-      <c r="E168" t="s">
+      <c r="F168" t="s">
         <v>1715</v>
       </c>
-      <c r="F168" t="s">
-        <v>1716</v>
-      </c>
       <c r="G168" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -71492,16 +72126,16 @@
         <v>915</v>
       </c>
       <c r="D169" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E169" t="s">
         <v>1714</v>
       </c>
-      <c r="E169" t="s">
+      <c r="F169" t="s">
         <v>1715</v>
       </c>
-      <c r="F169" t="s">
-        <v>1716</v>
-      </c>
       <c r="G169" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -71515,16 +72149,16 @@
         <v>920</v>
       </c>
       <c r="D170" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E170" t="s">
         <v>1714</v>
       </c>
-      <c r="E170" t="s">
+      <c r="F170" t="s">
         <v>1715</v>
       </c>
-      <c r="F170" t="s">
-        <v>1716</v>
-      </c>
       <c r="G170" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -71538,16 +72172,16 @@
         <v>925</v>
       </c>
       <c r="D171" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E171" t="s">
         <v>1714</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>1715</v>
       </c>
-      <c r="F171" t="s">
-        <v>1716</v>
-      </c>
       <c r="G171" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -71561,16 +72195,16 @@
         <v>930</v>
       </c>
       <c r="D172" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E172" t="s">
         <v>1714</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
         <v>1715</v>
       </c>
-      <c r="F172" t="s">
-        <v>1716</v>
-      </c>
       <c r="G172" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -71584,16 +72218,16 @@
         <v>935</v>
       </c>
       <c r="D173" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E173" t="s">
         <v>1714</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>1715</v>
       </c>
-      <c r="F173" t="s">
-        <v>1716</v>
-      </c>
       <c r="G173" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -71607,16 +72241,16 @@
         <v>940</v>
       </c>
       <c r="D174" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E174" t="s">
         <v>1714</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
         <v>1715</v>
       </c>
-      <c r="F174" t="s">
-        <v>1716</v>
-      </c>
       <c r="G174" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -71630,16 +72264,16 @@
         <v>946</v>
       </c>
       <c r="D175" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E175" t="s">
         <v>1714</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>1715</v>
       </c>
-      <c r="F175" t="s">
-        <v>1716</v>
-      </c>
       <c r="G175" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -71653,16 +72287,16 @@
         <v>951</v>
       </c>
       <c r="D176" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E176" t="s">
         <v>1714</v>
       </c>
-      <c r="E176" t="s">
+      <c r="F176" t="s">
         <v>1715</v>
       </c>
-      <c r="F176" t="s">
-        <v>1716</v>
-      </c>
       <c r="G176" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -71676,16 +72310,16 @@
         <v>956</v>
       </c>
       <c r="D177" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E177" t="s">
         <v>1714</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>1715</v>
       </c>
-      <c r="F177" t="s">
-        <v>1716</v>
-      </c>
       <c r="G177" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -71699,16 +72333,16 @@
         <v>961</v>
       </c>
       <c r="D178" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E178" t="s">
         <v>1714</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>1715</v>
       </c>
-      <c r="F178" t="s">
-        <v>1716</v>
-      </c>
       <c r="G178" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -71722,16 +72356,16 @@
         <v>966</v>
       </c>
       <c r="D179" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E179" t="s">
         <v>1714</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F179" t="s">
         <v>1715</v>
       </c>
-      <c r="F179" t="s">
-        <v>1716</v>
-      </c>
       <c r="G179" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -71745,16 +72379,16 @@
         <v>972</v>
       </c>
       <c r="D180" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E180" t="s">
         <v>1714</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>1715</v>
       </c>
-      <c r="F180" t="s">
-        <v>1716</v>
-      </c>
       <c r="G180" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -71768,16 +72402,16 @@
         <v>977</v>
       </c>
       <c r="D181" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E181" t="s">
         <v>1714</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>1715</v>
       </c>
-      <c r="F181" t="s">
-        <v>1716</v>
-      </c>
       <c r="G181" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -71791,16 +72425,16 @@
         <v>983</v>
       </c>
       <c r="D182" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E182" t="s">
         <v>1714</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
         <v>1715</v>
       </c>
-      <c r="F182" t="s">
-        <v>1716</v>
-      </c>
       <c r="G182" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -71814,16 +72448,16 @@
         <v>989</v>
       </c>
       <c r="D183" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E183" t="s">
         <v>1714</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
         <v>1715</v>
       </c>
-      <c r="F183" t="s">
-        <v>1716</v>
-      </c>
       <c r="G183" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -71837,16 +72471,16 @@
         <v>994</v>
       </c>
       <c r="D184" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E184" t="s">
         <v>1714</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
         <v>1715</v>
       </c>
-      <c r="F184" t="s">
-        <v>1716</v>
-      </c>
       <c r="G184" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -71860,16 +72494,16 @@
         <v>1001</v>
       </c>
       <c r="D185" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E185" t="s">
         <v>1714</v>
       </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
         <v>1715</v>
       </c>
-      <c r="F185" t="s">
-        <v>1716</v>
-      </c>
       <c r="G185" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -71883,16 +72517,16 @@
         <v>1008</v>
       </c>
       <c r="D186" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E186" t="s">
         <v>1714</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>1715</v>
       </c>
-      <c r="F186" t="s">
-        <v>1716</v>
-      </c>
       <c r="G186" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -71906,16 +72540,16 @@
         <v>1016</v>
       </c>
       <c r="D187" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E187" t="s">
         <v>1714</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>1715</v>
       </c>
-      <c r="F187" t="s">
-        <v>1716</v>
-      </c>
       <c r="G187" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -71929,16 +72563,16 @@
         <v>1023</v>
       </c>
       <c r="D188" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E188" t="s">
         <v>1714</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
         <v>1715</v>
       </c>
-      <c r="F188" t="s">
-        <v>1716</v>
-      </c>
       <c r="G188" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -71952,16 +72586,16 @@
         <v>1029</v>
       </c>
       <c r="D189" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E189" t="s">
         <v>1714</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
         <v>1715</v>
       </c>
-      <c r="F189" t="s">
-        <v>1716</v>
-      </c>
       <c r="G189" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -71975,16 +72609,16 @@
         <v>1036</v>
       </c>
       <c r="D190" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E190" t="s">
         <v>1714</v>
       </c>
-      <c r="E190" t="s">
+      <c r="F190" t="s">
         <v>1715</v>
       </c>
-      <c r="F190" t="s">
-        <v>1716</v>
-      </c>
       <c r="G190" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -71998,16 +72632,16 @@
         <v>1042</v>
       </c>
       <c r="D191" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E191" t="s">
         <v>1714</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
         <v>1715</v>
       </c>
-      <c r="F191" t="s">
-        <v>1716</v>
-      </c>
       <c r="G191" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -72021,16 +72655,16 @@
         <v>1047</v>
       </c>
       <c r="D192" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E192" t="s">
         <v>1714</v>
       </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
         <v>1715</v>
       </c>
-      <c r="F192" t="s">
-        <v>1716</v>
-      </c>
       <c r="G192" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -72044,16 +72678,16 @@
         <v>1056</v>
       </c>
       <c r="D193" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E193" t="s">
         <v>1714</v>
       </c>
-      <c r="E193" t="s">
+      <c r="F193" t="s">
         <v>1715</v>
       </c>
-      <c r="F193" t="s">
-        <v>1716</v>
-      </c>
       <c r="G193" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -72067,16 +72701,16 @@
         <v>1062</v>
       </c>
       <c r="D194" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E194" t="s">
         <v>1714</v>
       </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
         <v>1715</v>
       </c>
-      <c r="F194" t="s">
-        <v>1716</v>
-      </c>
       <c r="G194" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -72090,16 +72724,16 @@
         <v>1068</v>
       </c>
       <c r="D195" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E195" t="s">
         <v>1714</v>
       </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
         <v>1715</v>
       </c>
-      <c r="F195" t="s">
-        <v>1716</v>
-      </c>
       <c r="G195" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -72113,16 +72747,16 @@
         <v>1074</v>
       </c>
       <c r="D196" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E196" t="s">
         <v>1714</v>
       </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>1715</v>
       </c>
-      <c r="F196" t="s">
-        <v>1716</v>
-      </c>
       <c r="G196" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -72136,16 +72770,16 @@
         <v>1079</v>
       </c>
       <c r="D197" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E197" t="s">
         <v>1714</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
         <v>1715</v>
       </c>
-      <c r="F197" t="s">
-        <v>1716</v>
-      </c>
       <c r="G197" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -72159,16 +72793,16 @@
         <v>1084</v>
       </c>
       <c r="D198" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E198" t="s">
         <v>1714</v>
       </c>
-      <c r="E198" t="s">
+      <c r="F198" t="s">
         <v>1715</v>
       </c>
-      <c r="F198" t="s">
-        <v>1716</v>
-      </c>
       <c r="G198" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -72182,16 +72816,16 @@
         <v>1091</v>
       </c>
       <c r="D199" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E199" t="s">
         <v>1714</v>
       </c>
-      <c r="E199" t="s">
+      <c r="F199" t="s">
         <v>1715</v>
       </c>
-      <c r="F199" t="s">
-        <v>1716</v>
-      </c>
       <c r="G199" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -72205,16 +72839,16 @@
         <v>1097</v>
       </c>
       <c r="D200" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E200" t="s">
         <v>1714</v>
       </c>
-      <c r="E200" t="s">
+      <c r="F200" t="s">
         <v>1715</v>
       </c>
-      <c r="F200" t="s">
-        <v>1716</v>
-      </c>
       <c r="G200" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -72228,16 +72862,16 @@
         <v>1103</v>
       </c>
       <c r="D201" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E201" t="s">
         <v>1714</v>
       </c>
-      <c r="E201" t="s">
+      <c r="F201" t="s">
         <v>1715</v>
       </c>
-      <c r="F201" t="s">
-        <v>1716</v>
-      </c>
       <c r="G201" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -72251,16 +72885,16 @@
         <v>1109</v>
       </c>
       <c r="D202" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E202" t="s">
         <v>1714</v>
       </c>
-      <c r="E202" t="s">
+      <c r="F202" t="s">
         <v>1715</v>
       </c>
-      <c r="F202" t="s">
-        <v>1716</v>
-      </c>
       <c r="G202" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -72274,16 +72908,16 @@
         <v>1114</v>
       </c>
       <c r="D203" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E203" t="s">
         <v>1714</v>
       </c>
-      <c r="E203" t="s">
+      <c r="F203" t="s">
         <v>1715</v>
       </c>
-      <c r="F203" t="s">
-        <v>1716</v>
-      </c>
       <c r="G203" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -72297,16 +72931,16 @@
         <v>1121</v>
       </c>
       <c r="D204" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E204" t="s">
         <v>1714</v>
       </c>
-      <c r="E204" t="s">
+      <c r="F204" t="s">
         <v>1715</v>
       </c>
-      <c r="F204" t="s">
-        <v>1716</v>
-      </c>
       <c r="G204" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -72320,16 +72954,16 @@
         <v>1127</v>
       </c>
       <c r="D205" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E205" t="s">
         <v>1714</v>
       </c>
-      <c r="E205" t="s">
+      <c r="F205" t="s">
         <v>1715</v>
       </c>
-      <c r="F205" t="s">
-        <v>1716</v>
-      </c>
       <c r="G205" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -72343,16 +72977,16 @@
         <v>1134</v>
       </c>
       <c r="D206" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E206" t="s">
         <v>1714</v>
       </c>
-      <c r="E206" t="s">
+      <c r="F206" t="s">
         <v>1715</v>
       </c>
-      <c r="F206" t="s">
-        <v>1716</v>
-      </c>
       <c r="G206" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -72366,16 +73000,16 @@
         <v>1139</v>
       </c>
       <c r="D207" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E207" t="s">
         <v>1714</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" t="s">
         <v>1715</v>
       </c>
-      <c r="F207" t="s">
-        <v>1716</v>
-      </c>
       <c r="G207" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -72389,16 +73023,16 @@
         <v>1144</v>
       </c>
       <c r="D208" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E208" t="s">
         <v>1714</v>
       </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
         <v>1715</v>
       </c>
-      <c r="F208" t="s">
-        <v>1716</v>
-      </c>
       <c r="G208" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -72412,16 +73046,16 @@
         <v>1149</v>
       </c>
       <c r="D209" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E209" t="s">
         <v>1714</v>
       </c>
-      <c r="E209" t="s">
+      <c r="F209" t="s">
         <v>1715</v>
       </c>
-      <c r="F209" t="s">
-        <v>1716</v>
-      </c>
       <c r="G209" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -72435,16 +73069,16 @@
         <v>1154</v>
       </c>
       <c r="D210" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E210" t="s">
         <v>1714</v>
       </c>
-      <c r="E210" t="s">
+      <c r="F210" t="s">
         <v>1715</v>
       </c>
-      <c r="F210" t="s">
-        <v>1716</v>
-      </c>
       <c r="G210" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -72458,16 +73092,16 @@
         <v>1159</v>
       </c>
       <c r="D211" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E211" t="s">
         <v>1714</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" t="s">
         <v>1715</v>
       </c>
-      <c r="F211" t="s">
-        <v>1716</v>
-      </c>
       <c r="G211" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -72481,16 +73115,16 @@
         <v>1167</v>
       </c>
       <c r="D212" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E212" t="s">
         <v>1714</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>1715</v>
       </c>
-      <c r="F212" t="s">
-        <v>1716</v>
-      </c>
       <c r="G212" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -72504,16 +73138,16 @@
         <v>1172</v>
       </c>
       <c r="D213" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E213" t="s">
         <v>1714</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" t="s">
         <v>1715</v>
       </c>
-      <c r="F213" t="s">
-        <v>1716</v>
-      </c>
       <c r="G213" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -72527,16 +73161,16 @@
         <v>1177</v>
       </c>
       <c r="D214" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E214" t="s">
         <v>1714</v>
       </c>
-      <c r="E214" t="s">
+      <c r="F214" t="s">
         <v>1715</v>
       </c>
-      <c r="F214" t="s">
-        <v>1716</v>
-      </c>
       <c r="G214" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -72550,16 +73184,16 @@
         <v>1184</v>
       </c>
       <c r="D215" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E215" t="s">
         <v>1714</v>
       </c>
-      <c r="E215" t="s">
+      <c r="F215" t="s">
         <v>1715</v>
       </c>
-      <c r="F215" t="s">
-        <v>1716</v>
-      </c>
       <c r="G215" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -72573,16 +73207,16 @@
         <v>1191</v>
       </c>
       <c r="D216" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E216" t="s">
         <v>1714</v>
       </c>
-      <c r="E216" t="s">
+      <c r="F216" t="s">
         <v>1715</v>
       </c>
-      <c r="F216" t="s">
-        <v>1716</v>
-      </c>
       <c r="G216" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -72596,16 +73230,16 @@
         <v>1196</v>
       </c>
       <c r="D217" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E217" t="s">
         <v>1714</v>
       </c>
-      <c r="E217" t="s">
+      <c r="F217" t="s">
         <v>1715</v>
       </c>
-      <c r="F217" t="s">
-        <v>1716</v>
-      </c>
       <c r="G217" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -72619,16 +73253,16 @@
         <v>1201</v>
       </c>
       <c r="D218" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E218" t="s">
         <v>1714</v>
       </c>
-      <c r="E218" t="s">
+      <c r="F218" t="s">
         <v>1715</v>
       </c>
-      <c r="F218" t="s">
-        <v>1716</v>
-      </c>
       <c r="G218" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -72642,16 +73276,16 @@
         <v>1206</v>
       </c>
       <c r="D219" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E219" t="s">
         <v>1714</v>
       </c>
-      <c r="E219" t="s">
+      <c r="F219" t="s">
         <v>1715</v>
       </c>
-      <c r="F219" t="s">
-        <v>1716</v>
-      </c>
       <c r="G219" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -72665,16 +73299,16 @@
         <v>1212</v>
       </c>
       <c r="D220" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E220" t="s">
         <v>1714</v>
       </c>
-      <c r="E220" t="s">
+      <c r="F220" t="s">
         <v>1715</v>
       </c>
-      <c r="F220" t="s">
-        <v>1716</v>
-      </c>
       <c r="G220" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -72688,16 +73322,16 @@
         <v>1217</v>
       </c>
       <c r="D221" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E221" t="s">
         <v>1714</v>
       </c>
-      <c r="E221" t="s">
+      <c r="F221" t="s">
         <v>1715</v>
       </c>
-      <c r="F221" t="s">
-        <v>1716</v>
-      </c>
       <c r="G221" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -72711,16 +73345,16 @@
         <v>1222</v>
       </c>
       <c r="D222" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E222" t="s">
         <v>1714</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>1715</v>
       </c>
-      <c r="F222" t="s">
-        <v>1716</v>
-      </c>
       <c r="G222" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -72734,16 +73368,16 @@
         <v>1227</v>
       </c>
       <c r="D223" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E223" t="s">
         <v>1714</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
         <v>1715</v>
       </c>
-      <c r="F223" t="s">
-        <v>1716</v>
-      </c>
       <c r="G223" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -72757,16 +73391,16 @@
         <v>1233</v>
       </c>
       <c r="D224" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E224" t="s">
         <v>1714</v>
       </c>
-      <c r="E224" t="s">
+      <c r="F224" t="s">
         <v>1715</v>
       </c>
-      <c r="F224" t="s">
-        <v>1716</v>
-      </c>
       <c r="G224" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -72780,16 +73414,16 @@
         <v>1238</v>
       </c>
       <c r="D225" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E225" t="s">
         <v>1714</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
         <v>1715</v>
       </c>
-      <c r="F225" t="s">
-        <v>1716</v>
-      </c>
       <c r="G225" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -72803,16 +73437,16 @@
         <v>1243</v>
       </c>
       <c r="D226" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E226" t="s">
         <v>1714</v>
       </c>
-      <c r="E226" t="s">
+      <c r="F226" t="s">
         <v>1715</v>
       </c>
-      <c r="F226" t="s">
-        <v>1716</v>
-      </c>
       <c r="G226" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -72826,16 +73460,16 @@
         <v>1248</v>
       </c>
       <c r="D227" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E227" t="s">
         <v>1714</v>
       </c>
-      <c r="E227" t="s">
+      <c r="F227" t="s">
         <v>1715</v>
       </c>
-      <c r="F227" t="s">
-        <v>1716</v>
-      </c>
       <c r="G227" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -72849,16 +73483,16 @@
         <v>1253</v>
       </c>
       <c r="D228" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E228" t="s">
         <v>1714</v>
       </c>
-      <c r="E228" t="s">
+      <c r="F228" t="s">
         <v>1715</v>
       </c>
-      <c r="F228" t="s">
-        <v>1716</v>
-      </c>
       <c r="G228" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -72872,16 +73506,16 @@
         <v>1259</v>
       </c>
       <c r="D229" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E229" t="s">
         <v>1714</v>
       </c>
-      <c r="E229" t="s">
+      <c r="F229" t="s">
         <v>1715</v>
       </c>
-      <c r="F229" t="s">
-        <v>1716</v>
-      </c>
       <c r="G229" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -72895,16 +73529,16 @@
         <v>1264</v>
       </c>
       <c r="D230" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E230" t="s">
         <v>1714</v>
       </c>
-      <c r="E230" t="s">
+      <c r="F230" t="s">
         <v>1715</v>
       </c>
-      <c r="F230" t="s">
-        <v>1716</v>
-      </c>
       <c r="G230" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -72918,16 +73552,16 @@
         <v>1270</v>
       </c>
       <c r="D231" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E231" t="s">
         <v>1714</v>
       </c>
-      <c r="E231" t="s">
+      <c r="F231" t="s">
         <v>1715</v>
       </c>
-      <c r="F231" t="s">
-        <v>1716</v>
-      </c>
       <c r="G231" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -72941,16 +73575,16 @@
         <v>1275</v>
       </c>
       <c r="D232" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E232" t="s">
         <v>1714</v>
       </c>
-      <c r="E232" t="s">
+      <c r="F232" t="s">
         <v>1715</v>
       </c>
-      <c r="F232" t="s">
-        <v>1716</v>
-      </c>
       <c r="G232" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -72964,16 +73598,16 @@
         <v>1280</v>
       </c>
       <c r="D233" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E233" t="s">
         <v>1714</v>
       </c>
-      <c r="E233" t="s">
+      <c r="F233" t="s">
         <v>1715</v>
       </c>
-      <c r="F233" t="s">
-        <v>1716</v>
-      </c>
       <c r="G233" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -72987,16 +73621,16 @@
         <v>1286</v>
       </c>
       <c r="D234" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E234" t="s">
         <v>1714</v>
       </c>
-      <c r="E234" t="s">
+      <c r="F234" t="s">
         <v>1715</v>
       </c>
-      <c r="F234" t="s">
-        <v>1716</v>
-      </c>
       <c r="G234" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -73010,16 +73644,16 @@
         <v>1292</v>
       </c>
       <c r="D235" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E235" t="s">
         <v>1714</v>
       </c>
-      <c r="E235" t="s">
+      <c r="F235" t="s">
         <v>1715</v>
       </c>
-      <c r="F235" t="s">
-        <v>1716</v>
-      </c>
       <c r="G235" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -73033,16 +73667,16 @@
         <v>1298</v>
       </c>
       <c r="D236" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E236" t="s">
         <v>1714</v>
       </c>
-      <c r="E236" t="s">
+      <c r="F236" t="s">
         <v>1715</v>
       </c>
-      <c r="F236" t="s">
-        <v>1716</v>
-      </c>
       <c r="G236" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -73056,33 +73690,169 @@
         <v>1304</v>
       </c>
       <c r="D237" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E237" t="s">
         <v>1714</v>
       </c>
-      <c r="E237" t="s">
+      <c r="F237" t="s">
         <v>1715</v>
       </c>
-      <c r="F237" t="s">
-        <v>1716</v>
-      </c>
       <c r="G237" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="B238" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C238" t="s">
         <v>1807</v>
       </c>
-      <c r="C238" t="s">
-        <v>1808</v>
-      </c>
       <c r="D238" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="G238" t="s">
-        <v>1714</v>
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C239" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G239" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B240" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C240" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D240" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G240" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C241" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G241" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B242" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C242" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D242" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G242" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C243" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G243" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C244" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D244" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G244" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C245" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G245" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C246" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D246" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G246" t="s">
+        <v>1713</v>
       </c>
     </row>
   </sheetData>
@@ -73103,19 +73873,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>1725</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>1726</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1727</v>
       </c>
     </row>
   </sheetData>
@@ -73133,7 +73903,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20">
       <c r="A1" s="1" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -73142,24 +73912,24 @@
     </row>
     <row r="3" spans="1:5" ht="56">
       <c r="A3" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1729</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>1730</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>1731</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>1732</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1733</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B4" s="32">
         <v>3000</v>
@@ -73171,12 +73941,12 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="B5" s="32">
         <v>3000</v>
@@ -73188,29 +73958,29 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B6" s="32">
+        <v>0</v>
+      </c>
+      <c r="C6" s="32">
+        <v>0</v>
+      </c>
+      <c r="D6" s="32">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
         <v>1737</v>
-      </c>
-      <c r="B6" s="32">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32">
-        <v>0</v>
-      </c>
-      <c r="D6" s="32">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
     </row>
   </sheetData>
@@ -73241,49 +74011,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="N1" s="54" t="s">
         <v>1740</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="N1" s="54" t="s">
-        <v>1741</v>
       </c>
       <c r="O1" s="54"/>
       <c r="P1" s="54"/>
     </row>
     <row r="2" spans="1:16" ht="30" customHeight="1">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="66" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="N2" s="54" t="s">
         <v>1742</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="N2" s="54" t="s">
+      <c r="O2" s="54" t="s">
         <v>1743</v>
       </c>
-      <c r="O2" s="54" t="s">
+      <c r="P2" s="54" t="s">
         <v>1744</v>
-      </c>
-      <c r="P2" s="54" t="s">
-        <v>1745</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -73296,25 +74066,25 @@
         <v>Lavandina</v>
       </c>
       <c r="P3" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="67" t="s">
         <v>1746</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="66" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="H4" s="67" t="s">
         <v>1747</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="H4" s="66" t="s">
-        <v>1748</v>
-      </c>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
       <c r="N4" t="str">
         <f>CATÁLOGOS!B7</f>
         <v>🍽️ Cocina</v>
@@ -73324,18 +74094,18 @@
         <v>Detergente concentrado</v>
       </c>
       <c r="P4" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25">
+      <c r="A5" s="49" t="s">
         <v>1749</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="49" t="s">
-        <v>1750</v>
-      </c>
       <c r="B5" s="50" t="s">
-        <v>1807</v>
+        <v>1834</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="I5" s="50"/>
       <c r="N5" t="str">
@@ -73347,18 +74117,18 @@
         <v>Detergente listo para usar</v>
       </c>
       <c r="P5" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="49" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H6" s="49" t="s">
         <v>1752</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>1367</v>
-      </c>
-      <c r="H6" s="49" t="s">
-        <v>1753</v>
       </c>
       <c r="I6" s="50"/>
       <c r="N6" t="str">
@@ -73370,18 +74140,18 @@
         <v>Lava-vajillas concentrado</v>
       </c>
       <c r="P6" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="49" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H7" s="49" t="s">
         <v>1755</v>
-      </c>
-      <c r="B7" s="50" t="s">
-        <v>1368</v>
-      </c>
-      <c r="H7" s="49" t="s">
-        <v>1756</v>
       </c>
       <c r="I7" s="50"/>
       <c r="N7" t="str">
@@ -73393,18 +74163,18 @@
         <v>Suavizante</v>
       </c>
       <c r="P7" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="49" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>1806</v>
+        <v>122</v>
       </c>
       <c r="H8" s="49" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="I8" s="50"/>
       <c r="N8" t="str">
@@ -73421,13 +74191,13 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="49" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>1805</v>
+        <v>1828</v>
       </c>
       <c r="H9" s="49" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="I9" s="50"/>
       <c r="N9" t="str">
@@ -73439,16 +74209,16 @@
         <v>Perfumes para ropa</v>
       </c>
       <c r="P9" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="42" customHeight="1">
       <c r="A10" s="49" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="B10" s="50"/>
       <c r="H10" s="49" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="I10" s="50"/>
       <c r="N10" t="str">
@@ -73460,18 +74230,18 @@
         <v>Desengrasantes</v>
       </c>
       <c r="P10" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="42" customHeight="1">
       <c r="A11" s="49" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>1760</v>
+        <v>1796</v>
       </c>
       <c r="H11" s="49" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="I11" s="50"/>
       <c r="N11" t="str">
@@ -73483,16 +74253,16 @@
         <v>Rejillas y repasadores</v>
       </c>
       <c r="P11" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="49" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B12" s="50"/>
       <c r="H12" s="49" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="I12" s="50"/>
       <c r="N12" t="str">
@@ -73504,16 +74274,16 @@
         <v>Trapos de piso</v>
       </c>
       <c r="P12" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="49" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="B13" s="50"/>
       <c r="H13" s="49" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="I13" s="50"/>
       <c r="N13" t="str">
@@ -73525,18 +74295,16 @@
         <v>Escobas y escobillones</v>
       </c>
       <c r="P13" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="42" customHeight="1">
       <c r="A14" s="49" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B14" s="50"/>
+      <c r="H14" s="49" t="s">
         <v>1770</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="49" t="s">
-        <v>1771</v>
       </c>
       <c r="I14" s="50"/>
       <c r="N14">
@@ -73548,16 +74316,18 @@
         <v>Bruja</v>
       </c>
       <c r="P14" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="42" customHeight="1">
       <c r="A15" s="49" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>1834</v>
+      </c>
+      <c r="H15" s="49" t="s">
         <v>1773</v>
-      </c>
-      <c r="B15" s="50"/>
-      <c r="H15" s="49" t="s">
-        <v>1774</v>
       </c>
       <c r="I15" s="50"/>
       <c r="N15">
@@ -73569,16 +74339,18 @@
         <v>Esponja</v>
       </c>
       <c r="P15" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="75">
+      <c r="A16" s="49" t="s">
         <v>1775</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="49" t="s">
+      <c r="B16" s="50" t="s">
+        <v>1835</v>
+      </c>
+      <c r="H16" s="49" t="s">
         <v>1776</v>
-      </c>
-      <c r="B16" s="50"/>
-      <c r="H16" s="49" t="s">
-        <v>1777</v>
       </c>
       <c r="I16" s="50"/>
       <c r="N16">
@@ -73590,18 +74362,18 @@
         <v>Silicona</v>
       </c>
       <c r="P16" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="49" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="B17" s="50">
-        <v>230</v>
+        <v>10000</v>
       </c>
       <c r="H17" s="49" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="I17" s="50"/>
       <c r="N17">
@@ -73613,18 +74385,18 @@
         <v>Silicona en Aerosol</v>
       </c>
       <c r="P17" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="49" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>1358</v>
+        <v>34</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="I18" s="50"/>
       <c r="N18">
@@ -73636,16 +74408,16 @@
         <v>Shampoo Siliconado</v>
       </c>
       <c r="P18" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="49" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="B19" s="50"/>
       <c r="H19" s="49" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="I19" s="50" t="s">
         <v>33</v>
@@ -73659,18 +74431,18 @@
         <v>Mini Lata Walker</v>
       </c>
       <c r="P19" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="49" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="B20" s="50" t="s">
         <v>33</v>
       </c>
       <c r="H20" s="49" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="I20" s="50" t="s">
         <v>34</v>
@@ -73684,12 +74456,12 @@
         <v>Perfume en Lata Walker</v>
       </c>
       <c r="P20" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="49" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="B21" s="50" t="s">
         <v>34</v>
@@ -73703,7 +74475,7 @@
         <v>Cera</v>
       </c>
       <c r="P21" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -73716,24 +74488,24 @@
         <v>Limpia Tapizado en Aerosol</v>
       </c>
       <c r="P22" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="68" t="s">
         <v>1788</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="67" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="63"/>
+      <c r="K23" s="63"/>
+      <c r="L23" s="63"/>
       <c r="N23">
         <f>CATÁLOGOS!B26</f>
         <v>0</v>
@@ -73743,7 +74515,7 @@
         <v>Jabón líquido de manos</v>
       </c>
       <c r="P23" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -73751,10 +74523,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="52">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="D24" s="52" t="s">
         <v>33</v>
@@ -73768,21 +74540,21 @@
         <v>Difusores aromáticos</v>
       </c>
       <c r="P24" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="51" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B25" s="52" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C25" s="51" t="s">
         <v>1792</v>
       </c>
-      <c r="B25" s="52" t="s">
+      <c r="D25" s="52" t="s">
         <v>1809</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>1793</v>
-      </c>
-      <c r="D25" s="52" t="s">
-        <v>1810</v>
       </c>
       <c r="N25">
         <f>CATÁLOGOS!B28</f>
@@ -73793,18 +74565,18 @@
         <v>Promo 15 litros</v>
       </c>
       <c r="P25" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="51" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C26" s="51" t="s">
         <v>1795</v>
-      </c>
-      <c r="B26" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>1796</v>
       </c>
       <c r="D26" s="52"/>
       <c r="N26">
@@ -73816,18 +74588,18 @@
         <v>Promo 12 litros</v>
       </c>
       <c r="P26" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="51" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>26</v>
+        <v>1268</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="D27" s="52"/>
       <c r="N27">
@@ -73841,13 +74613,13 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="51" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B28" s="52" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C28" s="51" t="s">
         <v>1799</v>
-      </c>
-      <c r="B28" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>1800</v>
       </c>
       <c r="D28" s="52"/>
       <c r="N28">
@@ -73861,15 +74633,15 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="51" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C29" s="51" t="s">
         <v>1801</v>
       </c>
-      <c r="B29" s="53" t="s">
-        <v>1808</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>1802</v>
-      </c>
-      <c r="D29" s="75">
+      <c r="D29" s="61">
         <v>46121</v>
       </c>
       <c r="N29">
@@ -73892,20 +74664,20 @@
       </c>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="61" t="s">
-        <v>1803</v>
-      </c>
-      <c r="B31" s="62"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="62"/>
+      <c r="A31" s="62" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="63"/>
+      <c r="K31" s="63"/>
+      <c r="L31" s="63"/>
       <c r="N31">
         <f>CATÁLOGOS!B34</f>
         <v>0</v>
@@ -73916,20 +74688,20 @@
       </c>
     </row>
     <row r="32" spans="1:16" ht="24" customHeight="1">
-      <c r="A32" s="63" t="s">
-        <v>1804</v>
-      </c>
-      <c r="B32" s="62"/>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
-      <c r="L32" s="62"/>
+      <c r="A32" s="64" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B32" s="63"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
+      <c r="L32" s="63"/>
       <c r="N32">
         <f>CATÁLOGOS!B35</f>
         <v>0</v>
@@ -73940,18 +74712,18 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="24" customHeight="1">
-      <c r="A33" s="62"/>
-      <c r="B33" s="62"/>
-      <c r="C33" s="62"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="62"/>
-      <c r="H33" s="62"/>
-      <c r="I33" s="62"/>
-      <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
-      <c r="L33" s="62"/>
+      <c r="A33" s="63"/>
+      <c r="B33" s="63"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="63"/>
+      <c r="K33" s="63"/>
+      <c r="L33" s="63"/>
       <c r="N33">
         <f>CATÁLOGOS!B36</f>
         <v>0</v>
@@ -73962,18 +74734,18 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="24" customHeight="1">
-      <c r="A34" s="62"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="62"/>
-      <c r="J34" s="62"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="62"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="63"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="63"/>
+      <c r="K34" s="63"/>
+      <c r="L34" s="63"/>
       <c r="N34">
         <f>CATÁLOGOS!B37</f>
         <v>0</v>
@@ -73984,18 +74756,18 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="24" customHeight="1">
-      <c r="A35" s="62"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
+      <c r="A35" s="63"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
       <c r="N35">
         <f>CATÁLOGOS!B38</f>
         <v>0</v>

--- a/public/Plantilla_Quimica_Bethel.xlsx
+++ b/public/Plantilla_Quimica_Bethel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\QUIMICA - V3\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9E27BF-4DB6-4D3D-B697-916BDB1377C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25C2344-E0BA-4EC4-A200-1D6E47CA3827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="11500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6636" uniqueCount="1838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6744" uniqueCount="1858">
   <si>
     <t>CATÁLOGO DE PRODUCTOS · CARGA ADMINISTRATIVA</t>
   </si>
@@ -5546,13 +5546,73 @@
     <t>Papel de cocina pack de 8 rollos x 150m</t>
   </si>
   <si>
-    <t>Pack de 8 Rollos de 150 metros: mayor rendimiento en cada compra. Pre corte facilita el uso y evita desperdicios. Textura suave para una experiencia agradable y delicada</t>
-  </si>
-  <si>
     <t>VAR017.jpg</t>
   </si>
   <si>
     <t>VAR017</t>
+  </si>
+  <si>
+    <t>Secador Goma Negra 30 cm</t>
+  </si>
+  <si>
+    <t>Supy</t>
+  </si>
+  <si>
+    <t>Una herramienta imprescindible para mantener tus espacios limpios y seguros. Con una amplia cobertura y un diseño ergonómico</t>
+  </si>
+  <si>
+    <t>TDP009.jpg</t>
+  </si>
+  <si>
+    <t>TDP009</t>
+  </si>
+  <si>
+    <t>Secador Goma Negra 40 cm</t>
+  </si>
+  <si>
+    <t>TDP010.jpg</t>
+  </si>
+  <si>
+    <t>TDP010</t>
+  </si>
+  <si>
+    <t>Secador Goma Negra 50 cm</t>
+  </si>
+  <si>
+    <t>TDP011.jpg</t>
+  </si>
+  <si>
+    <t>TDP011</t>
+  </si>
+  <si>
+    <t>generico</t>
+  </si>
+  <si>
+    <t>Repuesto Secador de piso de madera de 80cm</t>
+  </si>
+  <si>
+    <t>TDP012.jpg</t>
+  </si>
+  <si>
+    <t>TDP012</t>
+  </si>
+  <si>
+    <t>Secador de piso doble goma 41cm</t>
+  </si>
+  <si>
+    <t>TDP013.jpg</t>
+  </si>
+  <si>
+    <t>TDP013</t>
+  </si>
+  <si>
+    <t>Sopapa Negra con cabo</t>
+  </si>
+  <si>
+    <t>APB006.jpg</t>
+  </si>
+  <si>
+    <t>APB006</t>
   </si>
 </sst>
 </file>
@@ -6117,7 +6177,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProductosAdmin" displayName="ProductosAdmin" ref="A4:U1015" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProductosAdmin" displayName="ProductosAdmin" ref="A4:U1021" totalsRowShown="0">
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CODIGO"/>
@@ -6146,8 +6206,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PreciosPorProducto" displayName="PreciosPorProducto" ref="A14:L261" totalsRowShown="0">
-  <autoFilter ref="A14:L261" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PreciosPorProducto" displayName="PreciosPorProducto" ref="A14:L267" totalsRowShown="0">
+  <autoFilter ref="A14:L267" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CODIGO"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="COSTO"/>
@@ -6411,7 +6471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1015"/>
+  <dimension ref="A1:U1021"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -38952,10 +39012,10 @@
         <v>244</v>
       </c>
       <c r="B1015" s="8" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="C1015" s="8" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="D1015" s="8"/>
       <c r="E1015" s="8"/>
@@ -38978,7 +39038,7 @@
         <v>122</v>
       </c>
       <c r="N1015" s="8" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="O1015" s="8" t="s">
         <v>1813</v>
@@ -38994,16 +39054,298 @@
         <v>34</v>
       </c>
     </row>
+    <row r="1016" spans="1:21">
+      <c r="A1016" s="7">
+        <v>245</v>
+      </c>
+      <c r="B1016" s="8" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C1016" s="8" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D1016" s="8"/>
+      <c r="E1016" s="8"/>
+      <c r="F1016" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1016" s="14"/>
+      <c r="H1016" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I1016" s="14"/>
+      <c r="J1016" s="8" t="s">
+        <v>1838</v>
+      </c>
+      <c r="K1016" s="8" t="s">
+        <v>1837</v>
+      </c>
+      <c r="L1016" s="8"/>
+      <c r="M1016" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1016" s="8" t="s">
+        <v>1840</v>
+      </c>
+      <c r="O1016" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1016" s="14"/>
+      <c r="Q1016" s="14"/>
+      <c r="R1016" s="17"/>
+      <c r="S1016" s="17"/>
+      <c r="T1016" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1016" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:21">
+      <c r="A1017" s="7">
+        <v>246</v>
+      </c>
+      <c r="B1017" s="8" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C1017" s="8" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D1017" s="8"/>
+      <c r="E1017" s="8"/>
+      <c r="F1017" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1017" s="14"/>
+      <c r="H1017" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I1017" s="14"/>
+      <c r="J1017" s="8" t="s">
+        <v>1838</v>
+      </c>
+      <c r="K1017" s="8" t="s">
+        <v>1842</v>
+      </c>
+      <c r="L1017" s="8"/>
+      <c r="M1017" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1017" s="8" t="s">
+        <v>1843</v>
+      </c>
+      <c r="O1017" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1017" s="14"/>
+      <c r="Q1017" s="14"/>
+      <c r="R1017" s="17"/>
+      <c r="S1017" s="17"/>
+      <c r="T1017" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1017" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:21">
+      <c r="A1018" s="7">
+        <v>247</v>
+      </c>
+      <c r="B1018" s="8" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C1018" s="8" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D1018" s="8"/>
+      <c r="E1018" s="8"/>
+      <c r="F1018" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1018" s="14"/>
+      <c r="H1018" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I1018" s="14"/>
+      <c r="J1018" s="8" t="s">
+        <v>1838</v>
+      </c>
+      <c r="K1018" s="8" t="s">
+        <v>1845</v>
+      </c>
+      <c r="L1018" s="8"/>
+      <c r="M1018" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1018" s="8" t="s">
+        <v>1846</v>
+      </c>
+      <c r="O1018" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1018" s="14"/>
+      <c r="Q1018" s="14"/>
+      <c r="R1018" s="17"/>
+      <c r="S1018" s="17"/>
+      <c r="T1018" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1018" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:21">
+      <c r="A1019" s="7">
+        <v>248</v>
+      </c>
+      <c r="B1019" s="8" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C1019" s="8" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D1019" s="8"/>
+      <c r="E1019" s="8"/>
+      <c r="F1019" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1019" s="14"/>
+      <c r="H1019" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I1019" s="14"/>
+      <c r="J1019" s="8" t="s">
+        <v>1848</v>
+      </c>
+      <c r="K1019" s="8" t="s">
+        <v>1849</v>
+      </c>
+      <c r="L1019" s="8"/>
+      <c r="M1019" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1019" s="8" t="s">
+        <v>1850</v>
+      </c>
+      <c r="O1019" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1019" s="14"/>
+      <c r="Q1019" s="14"/>
+      <c r="R1019" s="17"/>
+      <c r="S1019" s="17"/>
+      <c r="T1019" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1019" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:21">
+      <c r="A1020" s="7">
+        <v>249</v>
+      </c>
+      <c r="B1020" s="8" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C1020" s="8" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D1020" s="8"/>
+      <c r="E1020" s="8"/>
+      <c r="F1020" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1020" s="14"/>
+      <c r="H1020" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I1020" s="14"/>
+      <c r="J1020" s="8" t="s">
+        <v>1848</v>
+      </c>
+      <c r="K1020" s="8" t="s">
+        <v>1852</v>
+      </c>
+      <c r="L1020" s="8"/>
+      <c r="M1020" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1020" s="8" t="s">
+        <v>1853</v>
+      </c>
+      <c r="O1020" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1020" s="14"/>
+      <c r="Q1020" s="14"/>
+      <c r="R1020" s="17"/>
+      <c r="S1020" s="17"/>
+      <c r="T1020" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1020" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:21">
+      <c r="A1021" s="7">
+        <v>250</v>
+      </c>
+      <c r="B1021" s="8" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C1021" s="8" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D1021" s="8"/>
+      <c r="E1021" s="8"/>
+      <c r="F1021" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1021" s="14"/>
+      <c r="H1021" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="I1021" s="14"/>
+      <c r="J1021" s="8" t="s">
+        <v>1848</v>
+      </c>
+      <c r="K1021" s="8" t="s">
+        <v>1855</v>
+      </c>
+      <c r="L1021" s="8"/>
+      <c r="M1021" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1021" s="8" t="s">
+        <v>1856</v>
+      </c>
+      <c r="O1021" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="P1021" s="14"/>
+      <c r="Q1021" s="14"/>
+      <c r="R1021" s="17"/>
+      <c r="S1021" s="17"/>
+      <c r="T1021" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1021" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:U2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="T5:T1015" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="T5:T1021" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Activo,Inactivo"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="U5:U1015" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="U5:U1021" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -50770,7 +51112,7 @@
     </row>
     <row r="261" spans="1:12">
       <c r="A261" s="55" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B261" s="56">
         <v>10000</v>
@@ -50813,76 +51155,268 @@
       </c>
     </row>
     <row r="262" spans="1:12">
-      <c r="A262" s="5"/>
-      <c r="B262" s="21"/>
-      <c r="C262" s="22"/>
-      <c r="D262" s="22"/>
-      <c r="E262" s="22"/>
-      <c r="F262" s="25"/>
-      <c r="G262" s="25"/>
-      <c r="H262" s="22"/>
-      <c r="I262" s="22"/>
-      <c r="J262" s="27"/>
+      <c r="A262" s="55" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B262" s="56">
+        <v>1850</v>
+      </c>
+      <c r="C262" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D262" s="56"/>
+      <c r="E262" s="58">
+        <f t="shared" ref="E262" si="117">IF(A262="","",IF(C262="NO",0,IF(D262&lt;&gt;"",D262,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F262" s="58">
+        <f t="shared" ref="F262" si="118">IF(A262="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G262" s="58">
+        <f t="shared" ref="G262" si="119">IF(A262="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H262" s="59">
+        <f t="shared" ref="H262" si="120">IF(A262="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I262" s="59">
+        <f t="shared" ref="I262" si="121">IF(A262="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J262" s="58">
+        <f t="shared" ref="J262" si="122">IF(OR(A262="",B262=""),"",ROUND((B262+E262+F262+G262)/(1-H262-I262),-1))</f>
+        <v>2810</v>
+      </c>
+      <c r="K262" s="58">
+        <f t="shared" ref="K262" si="123">IF(J262="","",J262-B262-E262-F262-G262-(J262*H262))</f>
+        <v>935</v>
+      </c>
+      <c r="L262" s="60">
+        <f t="shared" ref="L262" si="124">IF(J262="","",K262/J262)</f>
+        <v>0.33274021352313166</v>
+      </c>
     </row>
     <row r="263" spans="1:12">
-      <c r="A263" s="5"/>
-      <c r="B263" s="21"/>
-      <c r="C263" s="22"/>
-      <c r="D263" s="22"/>
-      <c r="E263" s="22"/>
-      <c r="F263" s="25"/>
-      <c r="G263" s="25"/>
-      <c r="H263" s="22"/>
-      <c r="I263" s="22"/>
-      <c r="J263" s="27"/>
+      <c r="A263" s="55" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B263" s="56">
+        <v>2050</v>
+      </c>
+      <c r="C263" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D263" s="56"/>
+      <c r="E263" s="58">
+        <f t="shared" ref="E263" si="125">IF(A263="","",IF(C263="NO",0,IF(D263&lt;&gt;"",D263,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F263" s="58">
+        <f t="shared" ref="F263" si="126">IF(A263="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G263" s="58">
+        <f t="shared" ref="G263" si="127">IF(A263="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H263" s="59">
+        <f t="shared" ref="H263" si="128">IF(A263="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I263" s="59">
+        <f t="shared" ref="I263" si="129">IF(A263="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J263" s="58">
+        <f t="shared" ref="J263" si="130">IF(OR(A263="",B263=""),"",ROUND((B263+E263+F263+G263)/(1-H263-I263),-1))</f>
+        <v>3110</v>
+      </c>
+      <c r="K263" s="58">
+        <f t="shared" ref="K263" si="131">IF(J263="","",J263-B263-E263-F263-G263-(J263*H263))</f>
+        <v>1035</v>
+      </c>
+      <c r="L263" s="60">
+        <f t="shared" ref="L263" si="132">IF(J263="","",K263/J263)</f>
+        <v>0.33279742765273312</v>
+      </c>
     </row>
     <row r="264" spans="1:12">
-      <c r="A264" s="5"/>
-      <c r="B264" s="21"/>
-      <c r="C264" s="22"/>
-      <c r="D264" s="22"/>
-      <c r="E264" s="22"/>
-      <c r="F264" s="25"/>
-      <c r="G264" s="25"/>
-      <c r="H264" s="22"/>
-      <c r="I264" s="22"/>
-      <c r="J264" s="27"/>
+      <c r="A264" s="55" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B264" s="56">
+        <v>2600</v>
+      </c>
+      <c r="C264" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D264" s="56"/>
+      <c r="E264" s="58">
+        <f t="shared" ref="E264" si="133">IF(A264="","",IF(C264="NO",0,IF(D264&lt;&gt;"",D264,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F264" s="58">
+        <f t="shared" ref="F264" si="134">IF(A264="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G264" s="58">
+        <f t="shared" ref="G264" si="135">IF(A264="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H264" s="59">
+        <f t="shared" ref="H264" si="136">IF(A264="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I264" s="59">
+        <f t="shared" ref="I264" si="137">IF(A264="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J264" s="58">
+        <f t="shared" ref="J264" si="138">IF(OR(A264="",B264=""),"",ROUND((B264+E264+F264+G264)/(1-H264-I264),-1))</f>
+        <v>3940</v>
+      </c>
+      <c r="K264" s="58">
+        <f t="shared" ref="K264" si="139">IF(J264="","",J264-B264-E264-F264-G264-(J264*H264))</f>
+        <v>1315</v>
+      </c>
+      <c r="L264" s="60">
+        <f t="shared" ref="L264" si="140">IF(J264="","",K264/J264)</f>
+        <v>0.33375634517766495</v>
+      </c>
     </row>
     <row r="265" spans="1:12">
-      <c r="A265" s="5"/>
-      <c r="B265" s="21"/>
-      <c r="C265" s="22"/>
-      <c r="D265" s="22"/>
-      <c r="E265" s="22"/>
-      <c r="F265" s="25"/>
-      <c r="G265" s="25"/>
-      <c r="H265" s="22"/>
-      <c r="I265" s="22"/>
-      <c r="J265" s="27"/>
+      <c r="A265" s="55" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B265" s="56">
+        <v>8500</v>
+      </c>
+      <c r="C265" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D265" s="56"/>
+      <c r="E265" s="58">
+        <f t="shared" ref="E265" si="141">IF(A265="","",IF(C265="NO",0,IF(D265&lt;&gt;"",D265,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F265" s="58">
+        <f t="shared" ref="F265" si="142">IF(A265="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G265" s="58">
+        <f t="shared" ref="G265" si="143">IF(A265="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H265" s="59">
+        <f t="shared" ref="H265" si="144">IF(A265="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I265" s="59">
+        <f t="shared" ref="I265" si="145">IF(A265="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J265" s="58">
+        <f t="shared" ref="J265" si="146">IF(OR(A265="",B265=""),"",ROUND((B265+E265+F265+G265)/(1-H265-I265),-1))</f>
+        <v>12780</v>
+      </c>
+      <c r="K265" s="58">
+        <f t="shared" ref="K265" si="147">IF(J265="","",J265-B265-E265-F265-G265-(J265*H265))</f>
+        <v>4255</v>
+      </c>
+      <c r="L265" s="60">
+        <f t="shared" ref="L265" si="148">IF(J265="","",K265/J265)</f>
+        <v>0.33294209702660404</v>
+      </c>
     </row>
     <row r="266" spans="1:12">
-      <c r="A266" s="5"/>
-      <c r="B266" s="21"/>
-      <c r="C266" s="22"/>
-      <c r="D266" s="22"/>
-      <c r="E266" s="22"/>
-      <c r="F266" s="25"/>
-      <c r="G266" s="25"/>
-      <c r="H266" s="22"/>
-      <c r="I266" s="22"/>
-      <c r="J266" s="27"/>
+      <c r="A266" s="55" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B266" s="56">
+        <v>1250</v>
+      </c>
+      <c r="C266" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D266" s="56"/>
+      <c r="E266" s="58">
+        <f t="shared" ref="E266" si="149">IF(A266="","",IF(C266="NO",0,IF(D266&lt;&gt;"",D266,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F266" s="58">
+        <f t="shared" ref="F266" si="150">IF(A266="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G266" s="58">
+        <f t="shared" ref="G266" si="151">IF(A266="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H266" s="59">
+        <f t="shared" ref="H266" si="152">IF(A266="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I266" s="59">
+        <f t="shared" ref="I266" si="153">IF(A266="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J266" s="58">
+        <f t="shared" ref="J266" si="154">IF(OR(A266="",B266=""),"",ROUND((B266+E266+F266+G266)/(1-H266-I266),-1))</f>
+        <v>1910</v>
+      </c>
+      <c r="K266" s="58">
+        <f t="shared" ref="K266" si="155">IF(J266="","",J266-B266-E266-F266-G266-(J266*H266))</f>
+        <v>635</v>
+      </c>
+      <c r="L266" s="60">
+        <f t="shared" ref="L266" si="156">IF(J266="","",K266/J266)</f>
+        <v>0.33246073298429318</v>
+      </c>
     </row>
     <row r="267" spans="1:12">
-      <c r="A267" s="5"/>
-      <c r="B267" s="21"/>
-      <c r="C267" s="22"/>
-      <c r="D267" s="22"/>
-      <c r="E267" s="22"/>
-      <c r="F267" s="25"/>
-      <c r="G267" s="25"/>
-      <c r="H267" s="22"/>
-      <c r="I267" s="22"/>
-      <c r="J267" s="27"/>
+      <c r="A267" s="55" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B267" s="56">
+        <v>1550</v>
+      </c>
+      <c r="C267" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D267" s="56"/>
+      <c r="E267" s="58">
+        <f t="shared" ref="E267" si="157">IF(A267="","",IF(C267="NO",0,IF(D267&lt;&gt;"",D267,$B$11)))</f>
+        <v>0</v>
+      </c>
+      <c r="F267" s="58">
+        <f t="shared" ref="F267" si="158">IF(A267="","",$B$7/$B$6)</f>
+        <v>25</v>
+      </c>
+      <c r="G267" s="58">
+        <f t="shared" ref="G267" si="159">IF(A267="","",($B$8-$B$9)/$B$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H267" s="59">
+        <f t="shared" ref="H267" si="160">IF(A267="","",$B$10)</f>
+        <v>0</v>
+      </c>
+      <c r="I267" s="59">
+        <f t="shared" ref="I267" si="161">IF(A267="","",$B$5)</f>
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="J267" s="58">
+        <f t="shared" ref="J267" si="162">IF(OR(A267="",B267=""),"",ROUND((B267+E267+F267+G267)/(1-H267-I267),-1))</f>
+        <v>2360</v>
+      </c>
+      <c r="K267" s="58">
+        <f t="shared" ref="K267" si="163">IF(J267="","",J267-B267-E267-F267-G267-(J267*H267))</f>
+        <v>785</v>
+      </c>
+      <c r="L267" s="60">
+        <f t="shared" ref="L267" si="164">IF(J267="","",K267/J267)</f>
+        <v>0.3326271186440678</v>
+      </c>
     </row>
     <row r="268" spans="1:12">
       <c r="A268" s="5"/>
@@ -59855,7 +60389,7 @@
     <mergeCell ref="F4:J4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C15:C261" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="C15:C267" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"SÍ,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -67037,10 +67571,10 @@
         <v>33</v>
       </c>
       <c r="N233" s="6" t="s">
-        <v>1834</v>
+        <v>1855</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="234" spans="6:15">
@@ -68297,7 +68831,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H246"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:8" ht="20">
@@ -73840,18 +74374,120 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="B246" t="s">
         <v>1834</v>
       </c>
       <c r="C246" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="D246" t="s">
         <v>1713</v>
       </c>
       <c r="G246" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C247" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D247" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G247" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C248" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D248" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G248" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C249" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D249" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G249" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C250" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D250" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G250" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C251" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D251" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G251" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D252" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G252" t="s">
         <v>1713</v>
       </c>
     </row>
@@ -74097,12 +74733,12 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="25">
+    <row r="5" spans="1:16">
       <c r="A5" s="49" t="s">
         <v>1749</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>1834</v>
+        <v>1855</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>1749</v>
@@ -74125,7 +74761,7 @@
         <v>1751</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>1401</v>
+        <v>1367</v>
       </c>
       <c r="H6" s="49" t="s">
         <v>1752</v>
@@ -74148,7 +74784,7 @@
         <v>1754</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>1480</v>
+        <v>1447</v>
       </c>
       <c r="H7" s="49" t="s">
         <v>1755</v>
@@ -74194,7 +74830,7 @@
         <v>1758</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>1828</v>
+        <v>1848</v>
       </c>
       <c r="H9" s="49" t="s">
         <v>1758</v>
@@ -74238,7 +74874,7 @@
         <v>1762</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>1796</v>
+        <v>1748</v>
       </c>
       <c r="H11" s="49" t="s">
         <v>1762</v>
@@ -74324,7 +74960,7 @@
         <v>1772</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>1834</v>
+        <v>1855</v>
       </c>
       <c r="H15" s="49" t="s">
         <v>1773</v>
@@ -74342,12 +74978,12 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="75">
+    <row r="16" spans="1:16" ht="50">
       <c r="A16" s="49" t="s">
         <v>1775</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
       <c r="H16" s="49" t="s">
         <v>1776</v>
@@ -74370,7 +75006,7 @@
         <v>1776</v>
       </c>
       <c r="B17" s="50">
-        <v>10000</v>
+        <v>1550</v>
       </c>
       <c r="H17" s="49" t="s">
         <v>1778</v>
@@ -74523,7 +75159,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="52">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C24" s="51" t="s">
         <v>1782</v>
@@ -74548,7 +75184,7 @@
         <v>1791</v>
       </c>
       <c r="B25" s="52" t="s">
-        <v>1837</v>
+        <v>1857</v>
       </c>
       <c r="C25" s="51" t="s">
         <v>1792</v>
@@ -74573,7 +75209,7 @@
         <v>1794</v>
       </c>
       <c r="B26" s="52" t="s">
-        <v>1012</v>
+        <v>25</v>
       </c>
       <c r="C26" s="51" t="s">
         <v>1795</v>
@@ -74596,7 +75232,7 @@
         <v>1797</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>1268</v>
+        <v>970</v>
       </c>
       <c r="C27" s="51" t="s">
         <v>1767</v>
@@ -74636,7 +75272,7 @@
         <v>1800</v>
       </c>
       <c r="B29" s="53" t="s">
-        <v>1836</v>
+        <v>1856</v>
       </c>
       <c r="C29" s="51" t="s">
         <v>1801</v>
